--- a/data/Population_par_age (2).xlsx
+++ b/data/Population_par_age (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\utilisateur\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB62D574-3919-4109-B1E4-35D7BFC1EF17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D825C0-1BC7-4728-8C3D-C5545975BDB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3166" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2771" uniqueCount="90">
   <si>
     <t>TIME</t>
   </si>
@@ -289,7 +289,7 @@
     <t>Finlande</t>
   </si>
   <si>
-    <t>United Kingdom</t>
+    <t>Suède</t>
   </si>
 </sst>
 </file>
@@ -343,7 +343,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -366,11 +366,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB0B0B0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -395,6 +406,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
@@ -713,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AOT26"/>
+  <dimension ref="A1:AOT25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="11.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -72440,5479 +72454,2222 @@
         <v>777</v>
       </c>
     </row>
-    <row r="23" spans="1:1086" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="1:1086" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B23" s="7">
-        <v>547035</v>
-      </c>
-      <c r="C23" s="7">
-        <v>540501</v>
-      </c>
-      <c r="D23" s="7">
-        <v>540406</v>
-      </c>
-      <c r="E23" s="7">
-        <v>532998</v>
-      </c>
-      <c r="F23" s="7">
-        <v>522126</v>
-      </c>
-      <c r="G23" s="7">
-        <v>513792</v>
-      </c>
-      <c r="H23" s="7">
-        <v>514861</v>
-      </c>
-      <c r="I23" s="7">
-        <v>523614</v>
-      </c>
-      <c r="J23" s="7">
-        <v>528550</v>
-      </c>
-      <c r="K23" s="7">
-        <v>437217</v>
-      </c>
-      <c r="L23" s="7">
-        <v>335371</v>
-      </c>
-      <c r="M23" s="7">
-        <v>329506</v>
-      </c>
-      <c r="N23" s="7">
-        <v>342068</v>
-      </c>
-      <c r="O23" s="7">
-        <v>346044</v>
-      </c>
-      <c r="P23" s="7">
-        <v>336973</v>
-      </c>
-      <c r="Q23" s="7">
-        <v>313119</v>
-      </c>
-      <c r="R23" s="7">
-        <v>284149</v>
-      </c>
-      <c r="S23" s="7">
-        <v>255935</v>
-      </c>
-      <c r="T23" s="7">
-        <v>231666</v>
-      </c>
-      <c r="U23" s="7">
-        <v>207878</v>
-      </c>
-      <c r="V23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="W23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="X23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AE23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AF23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AG23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AH23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AK23" s="7">
-        <v>551441</v>
-      </c>
-      <c r="AL23" s="7">
-        <v>536845</v>
-      </c>
-      <c r="AM23" s="7">
-        <v>529317</v>
-      </c>
-      <c r="AN23" s="7">
-        <v>528316</v>
-      </c>
-      <c r="AO23" s="7">
-        <v>519783</v>
-      </c>
-      <c r="AP23" s="7">
-        <v>507777</v>
-      </c>
-      <c r="AQ23" s="7">
-        <v>498254</v>
-      </c>
-      <c r="AR23" s="7">
-        <v>497830</v>
-      </c>
-      <c r="AS23" s="7">
-        <v>504944</v>
-      </c>
-      <c r="AT23" s="7">
-        <v>506949</v>
-      </c>
-      <c r="AU23" s="7">
-        <v>418552</v>
-      </c>
-      <c r="AV23" s="7">
-        <v>320260</v>
-      </c>
-      <c r="AW23" s="7">
-        <v>312062</v>
-      </c>
-      <c r="AX23" s="7">
-        <v>322759</v>
-      </c>
-      <c r="AY23" s="7">
-        <v>324291</v>
-      </c>
-      <c r="AZ23" s="7">
-        <v>313669</v>
-      </c>
-      <c r="BA23" s="7">
-        <v>289320</v>
-      </c>
-      <c r="BB23" s="7">
-        <v>260677</v>
-      </c>
-      <c r="BC23" s="7">
-        <v>233068</v>
-      </c>
-      <c r="BD23" s="7">
-        <v>208621</v>
-      </c>
-      <c r="BE23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="BF23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="BG23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="BH23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="BI23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="BJ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="BK23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="BL23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="BM23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="BN23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="BO23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="BP23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="BQ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="BR23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="BS23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="BT23" s="7">
-        <v>554433</v>
-      </c>
-      <c r="BU23" s="7">
-        <v>541632</v>
-      </c>
-      <c r="BV23" s="7">
-        <v>526134</v>
-      </c>
-      <c r="BW23" s="7">
-        <v>517690</v>
-      </c>
-      <c r="BX23" s="7">
-        <v>515427</v>
-      </c>
-      <c r="BY23" s="7">
-        <v>505638</v>
-      </c>
-      <c r="BZ23" s="7">
-        <v>492572</v>
-      </c>
-      <c r="CA23" s="7">
-        <v>482075</v>
-      </c>
-      <c r="CB23" s="7">
-        <v>480050</v>
-      </c>
-      <c r="CC23" s="7">
-        <v>485331</v>
-      </c>
-      <c r="CD23" s="7">
-        <v>484998</v>
-      </c>
-      <c r="CE23" s="7">
-        <v>399358</v>
-      </c>
-      <c r="CF23" s="7">
-        <v>304593</v>
-      </c>
-      <c r="CG23" s="7">
-        <v>294358</v>
-      </c>
-      <c r="CH23" s="7">
-        <v>302620</v>
-      </c>
-      <c r="CI23" s="7">
-        <v>302058</v>
-      </c>
-      <c r="CJ23" s="7">
-        <v>290206</v>
-      </c>
-      <c r="CK23" s="7">
-        <v>265755</v>
-      </c>
-      <c r="CL23" s="7">
-        <v>237421</v>
-      </c>
-      <c r="CM23" s="7">
-        <v>210179</v>
-      </c>
-      <c r="CN23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="CO23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="CP23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="CQ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="CR23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="CS23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="CT23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="CU23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="CV23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="CW23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="CX23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="CY23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="CZ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="DA23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="DB23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="DC23" s="7">
-        <v>548564</v>
-      </c>
-      <c r="DD23" s="7">
-        <v>544798</v>
-      </c>
-      <c r="DE23" s="7">
-        <v>531176</v>
-      </c>
-      <c r="DF23" s="7">
-        <v>514893</v>
-      </c>
-      <c r="DG23" s="7">
-        <v>505339</v>
-      </c>
-      <c r="DH23" s="7">
-        <v>501597</v>
-      </c>
-      <c r="DI23" s="7">
-        <v>490683</v>
-      </c>
-      <c r="DJ23" s="7">
-        <v>476818</v>
-      </c>
-      <c r="DK23" s="7">
-        <v>464938</v>
-      </c>
-      <c r="DL23" s="7">
-        <v>461503</v>
-      </c>
-      <c r="DM23" s="7">
-        <v>465052</v>
-      </c>
-      <c r="DN23" s="7">
-        <v>462181</v>
-      </c>
-      <c r="DO23" s="7">
-        <v>379340</v>
-      </c>
-      <c r="DP23" s="7">
-        <v>288498</v>
-      </c>
-      <c r="DQ23" s="7">
-        <v>276105</v>
-      </c>
-      <c r="DR23" s="7">
-        <v>281810</v>
-      </c>
-      <c r="DS23" s="7">
-        <v>279264</v>
-      </c>
-      <c r="DT23" s="7">
-        <v>266620</v>
-      </c>
-      <c r="DU23" s="7">
-        <v>241805</v>
-      </c>
-      <c r="DV23" s="7">
-        <v>214158</v>
-      </c>
-      <c r="DW23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="DX23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="DY23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="DZ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="EA23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="EB23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="EC23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ED23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="EE23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="EF23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="EG23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="EH23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="EI23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="EJ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="EK23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="EL23" s="7">
-        <v>535941</v>
-      </c>
-      <c r="EM23" s="7">
-        <v>539512</v>
-      </c>
-      <c r="EN23" s="7">
-        <v>534658</v>
-      </c>
-      <c r="EO23" s="7">
-        <v>520437</v>
-      </c>
-      <c r="EP23" s="7">
-        <v>503125</v>
-      </c>
-      <c r="EQ23" s="7">
-        <v>492339</v>
-      </c>
-      <c r="ER23" s="7">
-        <v>487464</v>
-      </c>
-      <c r="ES23" s="7">
-        <v>475343</v>
-      </c>
-      <c r="ET23" s="7">
-        <v>460415</v>
-      </c>
-      <c r="EU23" s="7">
-        <v>447477</v>
-      </c>
-      <c r="EV23" s="7">
-        <v>442489</v>
-      </c>
-      <c r="EW23" s="7">
-        <v>444371</v>
-      </c>
-      <c r="EX23" s="7">
-        <v>438923</v>
-      </c>
-      <c r="EY23" s="7">
-        <v>359355</v>
-      </c>
-      <c r="EZ23" s="7">
-        <v>272490</v>
-      </c>
-      <c r="FA23" s="7">
-        <v>257866</v>
-      </c>
-      <c r="FB23" s="7">
-        <v>261141</v>
-      </c>
-      <c r="FC23" s="7">
-        <v>257045</v>
-      </c>
-      <c r="FD23" s="7">
-        <v>243221</v>
-      </c>
-      <c r="FE23" s="7">
-        <v>218829</v>
-      </c>
-      <c r="FF23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="FG23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="FH23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="FI23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="FJ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="FK23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="FL23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="FM23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="FN23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="FO23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="FP23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="FQ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="FR23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="FS23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="FT23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="FU23" s="7">
-        <v>527736</v>
-      </c>
-      <c r="FV23" s="7">
-        <v>527802</v>
-      </c>
-      <c r="FW23" s="7">
-        <v>529801</v>
-      </c>
-      <c r="FX23" s="7">
-        <v>524169</v>
-      </c>
-      <c r="FY23" s="7">
-        <v>509058</v>
-      </c>
-      <c r="FZ23" s="7">
-        <v>490737</v>
-      </c>
-      <c r="GA23" s="7">
-        <v>478883</v>
-      </c>
-      <c r="GB23" s="7">
-        <v>472543</v>
-      </c>
-      <c r="GC23" s="7">
-        <v>459284</v>
-      </c>
-      <c r="GD23" s="7">
-        <v>443376</v>
-      </c>
-      <c r="GE23" s="7">
-        <v>429248</v>
-      </c>
-      <c r="GF23" s="7">
-        <v>422906</v>
-      </c>
-      <c r="GG23" s="7">
-        <v>423134</v>
-      </c>
-      <c r="GH23" s="7">
-        <v>415259</v>
-      </c>
-      <c r="GI23" s="7">
-        <v>338798</v>
-      </c>
-      <c r="GJ23" s="7">
-        <v>256410</v>
-      </c>
-      <c r="GK23" s="7">
-        <v>239529</v>
-      </c>
-      <c r="GL23" s="7">
-        <v>240532</v>
-      </c>
-      <c r="GM23" s="7">
-        <v>234657</v>
-      </c>
-      <c r="GN23" s="7">
-        <v>220154</v>
-      </c>
-      <c r="GO23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="GP23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="GQ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="GR23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="GS23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="GT23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="GU23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="GV23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="GW23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="GX23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="GY23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="GZ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="HA23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="HB23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="HC23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="HD23" s="7">
-        <v>533121</v>
-      </c>
-      <c r="HE23" s="7">
-        <v>520138</v>
-      </c>
-      <c r="HF23" s="7">
-        <v>518999</v>
-      </c>
-      <c r="HG23" s="7">
-        <v>519926</v>
-      </c>
-      <c r="HH23" s="7">
-        <v>513126</v>
-      </c>
-      <c r="HI23" s="7">
-        <v>496988</v>
-      </c>
-      <c r="HJ23" s="7">
-        <v>477697</v>
-      </c>
-      <c r="HK23" s="7">
-        <v>464597</v>
-      </c>
-      <c r="HL23" s="7">
-        <v>456868</v>
-      </c>
-      <c r="HM23" s="7">
-        <v>442379</v>
-      </c>
-      <c r="HN23" s="7">
-        <v>425417</v>
-      </c>
-      <c r="HO23" s="7">
-        <v>410272</v>
-      </c>
-      <c r="HP23" s="7">
-        <v>402493</v>
-      </c>
-      <c r="HQ23" s="7">
-        <v>401019</v>
-      </c>
-      <c r="HR23" s="7">
-        <v>390549</v>
-      </c>
-      <c r="HS23" s="7">
-        <v>317784</v>
-      </c>
-      <c r="HT23" s="7">
-        <v>239792</v>
-      </c>
-      <c r="HU23" s="7">
-        <v>220665</v>
-      </c>
-      <c r="HV23" s="7">
-        <v>219425</v>
-      </c>
-      <c r="HW23" s="7">
-        <v>212006</v>
-      </c>
-      <c r="HX23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="HY23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="HZ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="IA23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="IB23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="IC23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ID23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="IE23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="IF23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="IG23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="IH23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="II23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="IJ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="IK23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="IL23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="IM23" s="7">
-        <v>544912</v>
-      </c>
-      <c r="IN23" s="7">
-        <v>525719</v>
-      </c>
-      <c r="IO23" s="7">
-        <v>512124</v>
-      </c>
-      <c r="IP23" s="7">
-        <v>510187</v>
-      </c>
-      <c r="IQ23" s="7">
-        <v>509674</v>
-      </c>
-      <c r="IR23" s="7">
-        <v>501469</v>
-      </c>
-      <c r="IS23" s="7">
-        <v>484498</v>
-      </c>
-      <c r="IT23" s="7">
-        <v>464267</v>
-      </c>
-      <c r="IU23" s="7">
-        <v>449971</v>
-      </c>
-      <c r="IV23" s="7">
-        <v>440861</v>
-      </c>
-      <c r="IW23" s="7">
-        <v>425246</v>
-      </c>
-      <c r="IX23" s="7">
-        <v>407466</v>
-      </c>
-      <c r="IY23" s="7">
-        <v>391205</v>
-      </c>
-      <c r="IZ23" s="7">
-        <v>382039</v>
-      </c>
-      <c r="JA23" s="7">
-        <v>379003</v>
-      </c>
-      <c r="JB23" s="7">
-        <v>366034</v>
-      </c>
-      <c r="JC23" s="7">
-        <v>296855</v>
-      </c>
-      <c r="JD23" s="7">
-        <v>223482</v>
-      </c>
-      <c r="JE23" s="7">
-        <v>202015</v>
-      </c>
-      <c r="JF23" s="7">
-        <v>198861</v>
-      </c>
-      <c r="JG23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="JH23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="JI23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="JJ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="JK23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="JL23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="JM23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="JN23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="JO23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="JP23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="JQ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="JR23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="JS23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="JT23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="JU23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="JV23" s="7">
-        <v>553970</v>
-      </c>
-      <c r="JW23" s="7">
-        <v>537112</v>
-      </c>
-      <c r="JX23" s="7">
-        <v>517422</v>
-      </c>
-      <c r="JY23" s="7">
-        <v>503450</v>
-      </c>
-      <c r="JZ23" s="7">
-        <v>500205</v>
-      </c>
-      <c r="KA23" s="7">
-        <v>498638</v>
-      </c>
-      <c r="KB23" s="7">
-        <v>489172</v>
-      </c>
-      <c r="KC23" s="7">
-        <v>471432</v>
-      </c>
-      <c r="KD23" s="7">
-        <v>450026</v>
-      </c>
-      <c r="KE23" s="7">
-        <v>434807</v>
-      </c>
-      <c r="KF23" s="7">
-        <v>424280</v>
-      </c>
-      <c r="KG23" s="7">
-        <v>407746</v>
-      </c>
-      <c r="KH23" s="7">
-        <v>388990</v>
-      </c>
-      <c r="KI23" s="7">
-        <v>371794</v>
-      </c>
-      <c r="KJ23" s="7">
-        <v>361638</v>
-      </c>
-      <c r="KK23" s="7">
-        <v>356381</v>
-      </c>
-      <c r="KL23" s="7">
-        <v>341366</v>
-      </c>
-      <c r="KM23" s="7">
-        <v>276730</v>
-      </c>
-      <c r="KN23" s="7">
-        <v>205917</v>
-      </c>
-      <c r="KO23" s="7">
-        <v>183982</v>
-      </c>
-      <c r="KP23" s="7">
-        <v>178927</v>
-      </c>
-      <c r="KQ23" s="7">
-        <v>169376</v>
-      </c>
-      <c r="KR23" s="7">
-        <v>154092</v>
-      </c>
-      <c r="KS23" s="7">
-        <v>132619</v>
-      </c>
-      <c r="KT23" s="7">
-        <v>110425</v>
-      </c>
-      <c r="KU23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="KV23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="KW23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="KX23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="KY23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="KZ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="LA23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="LB23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="LC23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="LD23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="LE23" s="7">
-        <v>561946</v>
-      </c>
-      <c r="LF23" s="7">
-        <v>545424</v>
-      </c>
-      <c r="LG23" s="7">
-        <v>528386</v>
-      </c>
-      <c r="LH23" s="7">
-        <v>508421</v>
-      </c>
-      <c r="LI23" s="7">
-        <v>493305</v>
-      </c>
-      <c r="LJ23" s="7">
-        <v>489365</v>
-      </c>
-      <c r="LK23" s="7">
-        <v>486647</v>
-      </c>
-      <c r="LL23" s="7">
-        <v>475882</v>
-      </c>
-      <c r="LM23" s="7">
-        <v>457222</v>
-      </c>
-      <c r="LN23" s="7">
-        <v>434924</v>
-      </c>
-      <c r="LO23" s="7">
-        <v>418633</v>
-      </c>
-      <c r="LP23" s="7">
-        <v>406614</v>
-      </c>
-      <c r="LQ23" s="7">
-        <v>389077</v>
-      </c>
-      <c r="LR23" s="7">
-        <v>369580</v>
-      </c>
-      <c r="LS23" s="7">
-        <v>351507</v>
-      </c>
-      <c r="LT23" s="7">
-        <v>339630</v>
-      </c>
-      <c r="LU23" s="7">
-        <v>333111</v>
-      </c>
-      <c r="LV23" s="7">
-        <v>315898</v>
-      </c>
-      <c r="LW23" s="7">
-        <v>254531</v>
-      </c>
-      <c r="LX23" s="7">
-        <v>188526</v>
-      </c>
-      <c r="LY23" s="7">
-        <v>165796</v>
-      </c>
-      <c r="LZ23" s="7">
-        <v>159312</v>
-      </c>
-      <c r="MA23" s="7">
-        <v>148845</v>
-      </c>
-      <c r="MB23" s="7">
-        <v>133877</v>
-      </c>
-      <c r="MC23" s="7">
-        <v>113212</v>
-      </c>
-      <c r="MD23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ME23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="MF23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="MG23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="MH23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="MI23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="MJ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="MK23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ML23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="MM23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="MN23" s="7">
-        <v>565831</v>
-      </c>
-      <c r="MO23" s="7">
-        <v>553337</v>
-      </c>
-      <c r="MP23" s="7">
-        <v>536521</v>
-      </c>
-      <c r="MQ23" s="7">
-        <v>519026</v>
-      </c>
-      <c r="MR23" s="7">
-        <v>498353</v>
-      </c>
-      <c r="MS23" s="7">
-        <v>482692</v>
-      </c>
-      <c r="MT23" s="7">
-        <v>477822</v>
-      </c>
-      <c r="MU23" s="7">
-        <v>473654</v>
-      </c>
-      <c r="MV23" s="7">
-        <v>461921</v>
-      </c>
-      <c r="MW23" s="7">
-        <v>442313</v>
-      </c>
-      <c r="MX23" s="7">
-        <v>419174</v>
-      </c>
-      <c r="MY23" s="7">
-        <v>401765</v>
-      </c>
-      <c r="MZ23" s="7">
-        <v>388335</v>
-      </c>
-      <c r="NA23" s="7">
-        <v>369905</v>
-      </c>
-      <c r="NB23" s="7">
-        <v>349444</v>
-      </c>
-      <c r="NC23" s="7">
-        <v>330501</v>
-      </c>
-      <c r="ND23" s="7">
-        <v>317204</v>
-      </c>
-      <c r="NE23" s="7">
-        <v>308632</v>
-      </c>
-      <c r="NF23" s="7">
-        <v>289757</v>
-      </c>
-      <c r="NG23" s="7">
-        <v>232112</v>
-      </c>
-      <c r="NH23" s="7">
-        <v>170706</v>
-      </c>
-      <c r="NI23" s="7">
-        <v>147426</v>
-      </c>
-      <c r="NJ23" s="7">
-        <v>139909</v>
-      </c>
-      <c r="NK23" s="7">
-        <v>129003</v>
-      </c>
-      <c r="NL23" s="7">
-        <v>114446</v>
-      </c>
-      <c r="NM23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="NN23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="NO23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="NP23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="NQ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="NR23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="NS23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="NT23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="NU23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="NV23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="NW23" s="7">
-        <v>562500</v>
-      </c>
-      <c r="NX23" s="7">
-        <v>557604</v>
-      </c>
-      <c r="NY23" s="7">
-        <v>544647</v>
-      </c>
-      <c r="NZ23" s="7">
-        <v>526983</v>
-      </c>
-      <c r="OA23" s="7">
-        <v>509130</v>
-      </c>
-      <c r="OB23" s="7">
-        <v>488245</v>
-      </c>
-      <c r="OC23" s="7">
-        <v>471571</v>
-      </c>
-      <c r="OD23" s="7">
-        <v>465538</v>
-      </c>
-      <c r="OE23" s="7">
-        <v>460392</v>
-      </c>
-      <c r="OF23" s="7">
-        <v>447482</v>
-      </c>
-      <c r="OG23" s="7">
-        <v>426991</v>
-      </c>
-      <c r="OH23" s="7">
-        <v>402914</v>
-      </c>
-      <c r="OI23" s="7">
-        <v>384468</v>
-      </c>
-      <c r="OJ23" s="7">
-        <v>369644</v>
-      </c>
-      <c r="OK23" s="7">
-        <v>350126</v>
-      </c>
-      <c r="OL23" s="7">
-        <v>329110</v>
-      </c>
-      <c r="OM23" s="7">
-        <v>309100</v>
-      </c>
-      <c r="ON23" s="7">
-        <v>294678</v>
-      </c>
-      <c r="OO23" s="7">
-        <v>284094</v>
-      </c>
-      <c r="OP23" s="7">
-        <v>263698</v>
-      </c>
-      <c r="OQ23" s="7">
-        <v>209964</v>
-      </c>
-      <c r="OR23" s="7">
-        <v>153013</v>
-      </c>
-      <c r="OS23" s="7">
-        <v>129815</v>
-      </c>
-      <c r="OT23" s="7">
-        <v>121299</v>
-      </c>
-      <c r="OU23" s="7">
-        <v>110257</v>
-      </c>
-      <c r="OV23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="OW23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="OX23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="OY23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="OZ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="PA23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="PB23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="PC23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="PD23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="PE23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="PF23" s="7">
-        <v>543929</v>
-      </c>
-      <c r="PG23" s="7">
-        <v>553949</v>
-      </c>
-      <c r="PH23" s="7">
-        <v>548577</v>
-      </c>
-      <c r="PI23" s="7">
-        <v>534986</v>
-      </c>
-      <c r="PJ23" s="7">
-        <v>516801</v>
-      </c>
-      <c r="PK23" s="7">
-        <v>498936</v>
-      </c>
-      <c r="PL23" s="7">
-        <v>477394</v>
-      </c>
-      <c r="PM23" s="7">
-        <v>459764</v>
-      </c>
-      <c r="PN23" s="7">
-        <v>452762</v>
-      </c>
-      <c r="PO23" s="7">
-        <v>446463</v>
-      </c>
-      <c r="PP23" s="7">
-        <v>432567</v>
-      </c>
-      <c r="PQ23" s="7">
-        <v>411022</v>
-      </c>
-      <c r="PR23" s="7">
-        <v>386250</v>
-      </c>
-      <c r="PS23" s="7">
-        <v>366557</v>
-      </c>
-      <c r="PT23" s="7">
-        <v>350572</v>
-      </c>
-      <c r="PU23" s="7">
-        <v>330439</v>
-      </c>
-      <c r="PV23" s="7">
-        <v>308506</v>
-      </c>
-      <c r="PW23" s="7">
-        <v>287888</v>
-      </c>
-      <c r="PX23" s="7">
-        <v>272324</v>
-      </c>
-      <c r="PY23" s="7">
-        <v>259852</v>
-      </c>
-      <c r="PZ23" s="7">
-        <v>238214</v>
-      </c>
-      <c r="QA23" s="7">
-        <v>188536</v>
-      </c>
-      <c r="QB23" s="7">
-        <v>136332</v>
-      </c>
-      <c r="QC23" s="7">
-        <v>113051</v>
-      </c>
-      <c r="QD23" s="7">
-        <v>103990</v>
-      </c>
-      <c r="QE23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="QF23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="QG23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="QH23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="QI23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="QJ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="QK23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="QL23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="QM23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="QN23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="QO23" s="7">
-        <v>547281</v>
-      </c>
-      <c r="QP23" s="7">
-        <v>535328</v>
-      </c>
-      <c r="QQ23" s="7">
-        <v>544785</v>
-      </c>
-      <c r="QR23" s="7">
-        <v>539134</v>
-      </c>
-      <c r="QS23" s="7">
-        <v>524870</v>
-      </c>
-      <c r="QT23" s="7">
-        <v>506548</v>
-      </c>
-      <c r="QU23" s="7">
-        <v>488163</v>
-      </c>
-      <c r="QV23" s="7">
-        <v>466077</v>
-      </c>
-      <c r="QW23" s="7">
-        <v>447578</v>
-      </c>
-      <c r="QX23" s="7">
-        <v>439501</v>
-      </c>
-      <c r="QY23" s="7">
-        <v>432161</v>
-      </c>
-      <c r="QZ23" s="7">
-        <v>417083</v>
-      </c>
-      <c r="RA23" s="7">
-        <v>394629</v>
-      </c>
-      <c r="RB23" s="7">
-        <v>369061</v>
-      </c>
-      <c r="RC23" s="7">
-        <v>348610</v>
-      </c>
-      <c r="RD23" s="7">
-        <v>331358</v>
-      </c>
-      <c r="RE23" s="7">
-        <v>310399</v>
-      </c>
-      <c r="RF23" s="7">
-        <v>287796</v>
-      </c>
-      <c r="RG23" s="7">
-        <v>266791</v>
-      </c>
-      <c r="RH23" s="7">
-        <v>249977</v>
-      </c>
-      <c r="RI23" s="7">
-        <v>236050</v>
-      </c>
-      <c r="RJ23" s="7">
-        <v>213366</v>
-      </c>
-      <c r="RK23" s="7">
-        <v>167669</v>
-      </c>
-      <c r="RL23" s="7">
-        <v>120465</v>
-      </c>
-      <c r="RM23" s="7">
-        <v>97452</v>
-      </c>
-      <c r="RN23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="RO23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="RP23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="RQ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="RR23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="RS23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="RT23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="RU23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="RV23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="RW23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="RX23" s="7">
-        <v>593423</v>
-      </c>
-      <c r="RY23" s="7">
-        <v>540166</v>
-      </c>
-      <c r="RZ23" s="7">
-        <v>527332</v>
-      </c>
-      <c r="SA23" s="7">
-        <v>536455</v>
-      </c>
-      <c r="SB23" s="7">
-        <v>530152</v>
-      </c>
-      <c r="SC23" s="7">
-        <v>515346</v>
-      </c>
-      <c r="SD23" s="7">
-        <v>496258</v>
-      </c>
-      <c r="SE23" s="7">
-        <v>477480</v>
-      </c>
-      <c r="SF23" s="7">
-        <v>454871</v>
-      </c>
-      <c r="SG23" s="7">
-        <v>435336</v>
-      </c>
-      <c r="SH23" s="7">
-        <v>426106</v>
-      </c>
-      <c r="SI23" s="7">
-        <v>417473</v>
-      </c>
-      <c r="SJ23" s="7">
-        <v>401285</v>
-      </c>
-      <c r="SK23" s="7">
-        <v>377919</v>
-      </c>
-      <c r="SL23" s="7">
-        <v>351722</v>
-      </c>
-      <c r="SM23" s="7">
-        <v>330086</v>
-      </c>
-      <c r="SN23" s="7">
-        <v>311712</v>
-      </c>
-      <c r="SO23" s="7">
-        <v>289833</v>
-      </c>
-      <c r="SP23" s="7">
-        <v>266896</v>
-      </c>
-      <c r="SQ23" s="7">
-        <v>245427</v>
-      </c>
-      <c r="SR23" s="7">
-        <v>227650</v>
-      </c>
-      <c r="SS23" s="7">
-        <v>212332</v>
-      </c>
-      <c r="ST23" s="7">
-        <v>189096</v>
-      </c>
-      <c r="SU23" s="7">
-        <v>147404</v>
-      </c>
-      <c r="SV23" s="7">
-        <v>105238</v>
-      </c>
-      <c r="SW23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="SX23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="SY23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="SZ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="TA23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="TB23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="TC23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="TD23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="TE23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="TF23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="TG23" s="7">
-        <v>636249</v>
-      </c>
-      <c r="TH23" s="7">
-        <v>586826</v>
-      </c>
-      <c r="TI23" s="7">
-        <v>533144</v>
-      </c>
-      <c r="TJ23" s="7">
-        <v>519400</v>
-      </c>
-      <c r="TK23" s="7">
-        <v>528000</v>
-      </c>
-      <c r="TL23" s="7">
-        <v>521046</v>
-      </c>
-      <c r="TM23" s="7">
-        <v>505480</v>
-      </c>
-      <c r="TN23" s="7">
-        <v>485657</v>
-      </c>
-      <c r="TO23" s="7">
-        <v>466331</v>
-      </c>
-      <c r="TP23" s="7">
-        <v>443139</v>
-      </c>
-      <c r="TQ23" s="7">
-        <v>422562</v>
-      </c>
-      <c r="TR23" s="7">
-        <v>412064</v>
-      </c>
-      <c r="TS23" s="7">
-        <v>402288</v>
-      </c>
-      <c r="TT23" s="7">
-        <v>384906</v>
-      </c>
-      <c r="TU23" s="7">
-        <v>360635</v>
-      </c>
-      <c r="TV23" s="7">
-        <v>333626</v>
-      </c>
-      <c r="TW23" s="7">
-        <v>310918</v>
-      </c>
-      <c r="TX23" s="7">
-        <v>291386</v>
-      </c>
-      <c r="TY23" s="7">
-        <v>269121</v>
-      </c>
-      <c r="TZ23" s="7">
-        <v>245640</v>
-      </c>
-      <c r="UA23" s="7">
-        <v>223776</v>
-      </c>
-      <c r="UB23" s="7">
-        <v>205380</v>
-      </c>
-      <c r="UC23" s="7">
-        <v>189097</v>
-      </c>
-      <c r="UD23" s="7">
-        <v>164987</v>
-      </c>
-      <c r="UE23" s="7">
-        <v>127850</v>
-      </c>
-      <c r="UF23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="UG23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="UH23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="UI23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="UJ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="UK23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="UL23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="UM23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="UN23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="UO23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="UP23" s="7">
-        <v>649217</v>
-      </c>
-      <c r="UQ23" s="7">
-        <v>629932</v>
-      </c>
-      <c r="UR23" s="7">
-        <v>579869</v>
-      </c>
-      <c r="US23" s="7">
-        <v>525707</v>
-      </c>
-      <c r="UT23" s="7">
-        <v>511022</v>
-      </c>
-      <c r="UU23" s="7">
-        <v>518960</v>
-      </c>
-      <c r="UV23" s="7">
-        <v>511507</v>
-      </c>
-      <c r="UW23" s="7">
-        <v>495022</v>
-      </c>
-      <c r="UX23" s="7">
-        <v>474416</v>
-      </c>
-      <c r="UY23" s="7">
-        <v>454537</v>
-      </c>
-      <c r="UZ23" s="7">
-        <v>430892</v>
-      </c>
-      <c r="VA23" s="7">
-        <v>409106</v>
-      </c>
-      <c r="VB23" s="7">
-        <v>397434</v>
-      </c>
-      <c r="VC23" s="7">
-        <v>386690</v>
-      </c>
-      <c r="VD23" s="7">
-        <v>367964</v>
-      </c>
-      <c r="VE23" s="7">
-        <v>342768</v>
-      </c>
-      <c r="VF23" s="7">
-        <v>314945</v>
-      </c>
-      <c r="VG23" s="7">
-        <v>291634</v>
-      </c>
-      <c r="VH23" s="7">
-        <v>271272</v>
-      </c>
-      <c r="VI23" s="7">
-        <v>248230</v>
-      </c>
-      <c r="VJ23" s="7">
-        <v>224515</v>
-      </c>
-      <c r="VK23" s="7">
-        <v>202522</v>
-      </c>
-      <c r="VL23" s="7">
-        <v>183616</v>
-      </c>
-      <c r="VM23" s="7">
-        <v>166670</v>
-      </c>
-      <c r="VN23" s="7">
-        <v>142282</v>
-      </c>
-      <c r="VO23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="VP23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="VQ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="VR23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="VS23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="VT23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="VU23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="VV23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="VW23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="VX23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="VY23" s="7">
-        <v>652172</v>
-      </c>
-      <c r="VZ23" s="7">
-        <v>642554</v>
-      </c>
-      <c r="WA23" s="7">
-        <v>623151</v>
-      </c>
-      <c r="WB23" s="7">
-        <v>572572</v>
-      </c>
-      <c r="WC23" s="7">
-        <v>517708</v>
-      </c>
-      <c r="WD23" s="7">
-        <v>501996</v>
-      </c>
-      <c r="WE23" s="7">
-        <v>509345</v>
-      </c>
-      <c r="WF23" s="7">
-        <v>501374</v>
-      </c>
-      <c r="WG23" s="7">
-        <v>484053</v>
-      </c>
-      <c r="WH23" s="7">
-        <v>462676</v>
-      </c>
-      <c r="WI23" s="7">
-        <v>442272</v>
-      </c>
-      <c r="WJ23" s="7">
-        <v>417984</v>
-      </c>
-      <c r="WK23" s="7">
-        <v>395108</v>
-      </c>
-      <c r="WL23" s="7">
-        <v>382498</v>
-      </c>
-      <c r="WM23" s="7">
-        <v>370349</v>
-      </c>
-      <c r="WN23" s="7">
-        <v>350534</v>
-      </c>
-      <c r="WO23" s="7">
-        <v>324543</v>
-      </c>
-      <c r="WP23" s="7">
-        <v>296278</v>
-      </c>
-      <c r="WQ23" s="7">
-        <v>272078</v>
-      </c>
-      <c r="WR23" s="7">
-        <v>250782</v>
-      </c>
-      <c r="WS23" s="7">
-        <v>227368</v>
-      </c>
-      <c r="WT23" s="7">
-        <v>203782</v>
-      </c>
-      <c r="WU23" s="7">
-        <v>181835</v>
-      </c>
-      <c r="WV23" s="7">
-        <v>162888</v>
-      </c>
-      <c r="WW23" s="7">
-        <v>145329</v>
-      </c>
-      <c r="WX23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="WY23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="WZ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="XA23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="XB23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="XC23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="XD23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="XE23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="XF23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="XG23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="XH23" s="7">
-        <v>748673</v>
-      </c>
-      <c r="XI23" s="7">
-        <v>645002</v>
-      </c>
-      <c r="XJ23" s="7">
-        <v>635803</v>
-      </c>
-      <c r="XK23" s="7">
-        <v>615311</v>
-      </c>
-      <c r="XL23" s="7">
-        <v>564457</v>
-      </c>
-      <c r="XM23" s="7">
-        <v>509027</v>
-      </c>
-      <c r="XN23" s="7">
-        <v>492725</v>
-      </c>
-      <c r="XO23" s="7">
-        <v>499320</v>
-      </c>
-      <c r="XP23" s="7">
-        <v>490656</v>
-      </c>
-      <c r="XQ23" s="7">
-        <v>472746</v>
-      </c>
-      <c r="XR23" s="7">
-        <v>450444</v>
-      </c>
-      <c r="XS23" s="7">
-        <v>429559</v>
-      </c>
-      <c r="XT23" s="7">
-        <v>404382</v>
-      </c>
-      <c r="XU23" s="7">
-        <v>380604</v>
-      </c>
-      <c r="XV23" s="7">
-        <v>367004</v>
-      </c>
-      <c r="XW23" s="7">
-        <v>353390</v>
-      </c>
-      <c r="XX23" s="7">
-        <v>332550</v>
-      </c>
-      <c r="XY23" s="7">
-        <v>305702</v>
-      </c>
-      <c r="XZ23" s="7">
-        <v>276943</v>
-      </c>
-      <c r="YA23" s="7">
-        <v>251858</v>
-      </c>
-      <c r="YB23" s="7">
-        <v>230140</v>
-      </c>
-      <c r="YC23" s="7">
-        <v>206561</v>
-      </c>
-      <c r="YD23" s="7">
-        <v>183180</v>
-      </c>
-      <c r="YE23" s="7">
-        <v>161519</v>
-      </c>
-      <c r="YF23" s="7">
-        <v>142350</v>
-      </c>
-      <c r="YG23" s="7">
-        <v>131169</v>
-      </c>
-      <c r="YH23" s="7">
-        <v>103165</v>
-      </c>
-      <c r="YI23" s="7">
-        <v>68577</v>
-      </c>
-      <c r="YJ23" s="7">
-        <v>48960</v>
-      </c>
-      <c r="YK23" s="7">
-        <v>39776</v>
-      </c>
-      <c r="YL23" s="7">
-        <v>32337</v>
-      </c>
-      <c r="YM23" s="7">
-        <v>24808</v>
-      </c>
-      <c r="YN23" s="7">
-        <v>17910</v>
-      </c>
-      <c r="YO23" s="7">
-        <v>12412</v>
-      </c>
-      <c r="YP23" s="7">
-        <v>8099</v>
-      </c>
-      <c r="YQ23" s="7">
-        <v>804154</v>
-      </c>
-      <c r="YR23" s="7">
-        <v>741294</v>
-      </c>
-      <c r="YS23" s="7">
-        <v>637981</v>
-      </c>
-      <c r="YT23" s="7">
-        <v>628035</v>
-      </c>
-      <c r="YU23" s="7">
-        <v>606818</v>
-      </c>
-      <c r="YV23" s="7">
-        <v>555826</v>
-      </c>
-      <c r="YW23" s="7">
-        <v>500267</v>
-      </c>
-      <c r="YX23" s="7">
-        <v>483157</v>
-      </c>
-      <c r="YY23" s="7">
-        <v>488712</v>
-      </c>
-      <c r="YZ23" s="7">
-        <v>479606</v>
-      </c>
-      <c r="ZA23" s="7">
-        <v>460637</v>
-      </c>
-      <c r="ZB23" s="7">
-        <v>437583</v>
-      </c>
-      <c r="ZC23" s="7">
-        <v>415895</v>
-      </c>
-      <c r="ZD23" s="7">
-        <v>389914</v>
-      </c>
-      <c r="ZE23" s="7">
-        <v>365465</v>
-      </c>
-      <c r="ZF23" s="7">
-        <v>350466</v>
-      </c>
-      <c r="ZG23" s="7">
-        <v>335441</v>
-      </c>
-      <c r="ZH23" s="7">
-        <v>313301</v>
-      </c>
-      <c r="ZI23" s="7">
-        <v>286044</v>
-      </c>
-      <c r="ZJ23" s="7">
-        <v>256530</v>
-      </c>
-      <c r="ZK23" s="7">
-        <v>231090</v>
-      </c>
-      <c r="ZL23" s="7">
-        <v>209022</v>
-      </c>
-      <c r="ZM23" s="7">
-        <v>185463</v>
-      </c>
-      <c r="ZN23" s="7">
-        <v>162481</v>
-      </c>
-      <c r="ZO23" s="7">
-        <v>140878</v>
-      </c>
-      <c r="ZP23" s="7">
-        <v>127802</v>
-      </c>
-      <c r="ZQ23" s="7">
-        <v>109089</v>
-      </c>
-      <c r="ZR23" s="7">
-        <v>84199</v>
-      </c>
-      <c r="ZS23" s="7">
-        <v>54794</v>
-      </c>
-      <c r="ZT23" s="7">
-        <v>38320</v>
-      </c>
-      <c r="ZU23" s="7">
-        <v>30391</v>
-      </c>
-      <c r="ZV23" s="7">
-        <v>24026</v>
-      </c>
-      <c r="ZW23" s="7">
-        <v>17855</v>
-      </c>
-      <c r="ZX23" s="7">
-        <v>12559</v>
-      </c>
-      <c r="ZY23" s="7">
-        <v>8388</v>
-      </c>
-      <c r="ZZ23" s="7">
-        <v>745953</v>
-      </c>
-      <c r="AAA23" s="7">
-        <v>796672</v>
-      </c>
-      <c r="AAB23" s="7">
-        <v>733771</v>
-      </c>
-      <c r="AAC23" s="7">
-        <v>630512</v>
-      </c>
-      <c r="AAD23" s="7">
-        <v>619761</v>
-      </c>
-      <c r="AAE23" s="7">
-        <v>597810</v>
-      </c>
-      <c r="AAF23" s="7">
-        <v>546730</v>
-      </c>
-      <c r="AAG23" s="7">
-        <v>490812</v>
-      </c>
-      <c r="AAH23" s="7">
-        <v>473163</v>
-      </c>
-      <c r="AAI23" s="7">
-        <v>477857</v>
-      </c>
-      <c r="AAJ23" s="7">
-        <v>467709</v>
-      </c>
-      <c r="AAK23" s="7">
-        <v>447902</v>
-      </c>
-      <c r="AAL23" s="7">
-        <v>424120</v>
-      </c>
-      <c r="AAM23" s="7">
-        <v>401539</v>
-      </c>
-      <c r="AAN23" s="7">
-        <v>374868</v>
-      </c>
-      <c r="AAO23" s="7">
-        <v>349499</v>
-      </c>
-      <c r="AAP23" s="7">
-        <v>333311</v>
-      </c>
-      <c r="AAQ23" s="7">
-        <v>316642</v>
-      </c>
-      <c r="AAR23" s="7">
-        <v>293702</v>
-      </c>
-      <c r="AAS23" s="7">
-        <v>265814</v>
-      </c>
-      <c r="AAT23" s="7">
-        <v>235971</v>
-      </c>
-      <c r="AAU23" s="7">
-        <v>210681</v>
-      </c>
-      <c r="AAV23" s="7">
-        <v>188253</v>
-      </c>
-      <c r="AAW23" s="7">
-        <v>164957</v>
-      </c>
-      <c r="AAX23" s="7">
-        <v>142300</v>
-      </c>
-      <c r="AAY23" s="7">
-        <v>125365</v>
-      </c>
-      <c r="AAZ23" s="7">
-        <v>107738</v>
-      </c>
-      <c r="ABA23" s="7">
-        <v>90056</v>
-      </c>
-      <c r="ABB23" s="7">
-        <v>68057</v>
-      </c>
-      <c r="ABC23" s="7">
-        <v>43300</v>
-      </c>
-      <c r="ABD23" s="7">
-        <v>29537</v>
-      </c>
-      <c r="ABE23" s="7">
-        <v>22737</v>
-      </c>
-      <c r="ABF23" s="7">
-        <v>17494</v>
-      </c>
-      <c r="ABG23" s="7">
-        <v>12661</v>
-      </c>
-      <c r="ABH23" s="7">
-        <v>8605</v>
-      </c>
-      <c r="ABI23" s="7">
-        <v>712202</v>
-      </c>
-      <c r="ABJ23" s="7">
-        <v>739148</v>
-      </c>
-      <c r="ABK23" s="7">
-        <v>788807</v>
-      </c>
-      <c r="ABL23" s="7">
-        <v>725557</v>
-      </c>
-      <c r="ABM23" s="7">
-        <v>622505</v>
-      </c>
-      <c r="ABN23" s="7">
-        <v>610786</v>
-      </c>
-      <c r="ABO23" s="7">
-        <v>588239</v>
-      </c>
-      <c r="ABP23" s="7">
-        <v>536679</v>
-      </c>
-      <c r="ABQ23" s="7">
-        <v>481036</v>
-      </c>
-      <c r="ABR23" s="7">
-        <v>462626</v>
-      </c>
-      <c r="ABS23" s="7">
-        <v>466097</v>
-      </c>
-      <c r="ABT23" s="7">
-        <v>454982</v>
-      </c>
-      <c r="ABU23" s="7">
-        <v>434110</v>
-      </c>
-      <c r="ABV23" s="7">
-        <v>409679</v>
-      </c>
-      <c r="ABW23" s="7">
-        <v>386246</v>
-      </c>
-      <c r="ABX23" s="7">
-        <v>358516</v>
-      </c>
-      <c r="ABY23" s="7">
-        <v>332521</v>
-      </c>
-      <c r="ABZ23" s="7">
-        <v>314959</v>
-      </c>
-      <c r="ACA23" s="7">
-        <v>296736</v>
-      </c>
-      <c r="ACB23" s="7">
-        <v>273042</v>
-      </c>
-      <c r="ACC23" s="7">
-        <v>244779</v>
-      </c>
-      <c r="ACD23" s="7">
-        <v>215095</v>
-      </c>
-      <c r="ACE23" s="7">
-        <v>189611</v>
-      </c>
-      <c r="ACF23" s="7">
-        <v>167190</v>
-      </c>
-      <c r="ACG23" s="7">
-        <v>144317</v>
-      </c>
-      <c r="ACH23" s="7">
-        <v>124984</v>
-      </c>
-      <c r="ACI23" s="7">
-        <v>105543</v>
-      </c>
-      <c r="ACJ23" s="7">
-        <v>88968</v>
-      </c>
-      <c r="ACK23" s="7">
-        <v>72763</v>
-      </c>
-      <c r="ACL23" s="7">
-        <v>53948</v>
-      </c>
-      <c r="ACM23" s="7">
-        <v>33365</v>
-      </c>
-      <c r="ACN23" s="7">
-        <v>22112</v>
-      </c>
-      <c r="ACO23" s="7">
-        <v>16547</v>
-      </c>
-      <c r="ACP23" s="7">
-        <v>12440</v>
-      </c>
-      <c r="ACQ23" s="7">
-        <v>8756</v>
-      </c>
-      <c r="ACR23" s="7">
-        <v>691650</v>
-      </c>
-      <c r="ACS23" s="7">
-        <v>705551</v>
-      </c>
-      <c r="ACT23" s="7">
-        <v>731786</v>
-      </c>
-      <c r="ACU23" s="7">
-        <v>780046</v>
-      </c>
-      <c r="ACV23" s="7">
-        <v>716522</v>
-      </c>
-      <c r="ACW23" s="7">
-        <v>613555</v>
-      </c>
-      <c r="ACX23" s="7">
-        <v>601064</v>
-      </c>
-      <c r="ACY23" s="7">
-        <v>577816</v>
-      </c>
-      <c r="ACZ23" s="7">
-        <v>525956</v>
-      </c>
-      <c r="ADA23" s="7">
-        <v>470224</v>
-      </c>
-      <c r="ADB23" s="7">
-        <v>451064</v>
-      </c>
-      <c r="ADC23" s="7">
-        <v>453264</v>
-      </c>
-      <c r="ADD23" s="7">
-        <v>440800</v>
-      </c>
-      <c r="ADE23" s="7">
-        <v>419141</v>
-      </c>
-      <c r="ADF23" s="7">
-        <v>394018</v>
-      </c>
-      <c r="ADG23" s="7">
-        <v>369334</v>
-      </c>
-      <c r="ADH23" s="7">
-        <v>340951</v>
-      </c>
-      <c r="ADI23" s="7">
-        <v>314193</v>
-      </c>
-      <c r="ADJ23" s="7">
-        <v>295085</v>
-      </c>
-      <c r="ADK23" s="7">
-        <v>275568</v>
-      </c>
-      <c r="ADL23" s="7">
-        <v>251292</v>
-      </c>
-      <c r="ADM23" s="7">
-        <v>222705</v>
-      </c>
-      <c r="ADN23" s="7">
-        <v>193325</v>
-      </c>
-      <c r="ADO23" s="7">
-        <v>168007</v>
-      </c>
-      <c r="ADP23" s="7">
-        <v>145964</v>
-      </c>
-      <c r="ADQ23" s="7">
-        <v>125360</v>
-      </c>
-      <c r="ADR23" s="7">
-        <v>104997</v>
-      </c>
-      <c r="ADS23" s="7">
-        <v>87048</v>
-      </c>
-      <c r="ADT23" s="7">
-        <v>71838</v>
-      </c>
-      <c r="ADU23" s="7">
-        <v>57403</v>
-      </c>
-      <c r="ADV23" s="7">
-        <v>41428</v>
-      </c>
-      <c r="ADW23" s="7">
-        <v>24954</v>
-      </c>
-      <c r="ADX23" s="7">
-        <v>16051</v>
-      </c>
-      <c r="ADY23" s="7">
-        <v>11687</v>
-      </c>
-      <c r="ADZ23" s="7">
-        <v>8538</v>
-      </c>
-      <c r="AEA23" s="7">
-        <v>677662</v>
-      </c>
-      <c r="AEB23" s="7">
-        <v>685079</v>
-      </c>
-      <c r="AEC23" s="7">
-        <v>698292</v>
-      </c>
-      <c r="AED23" s="7">
-        <v>723673</v>
-      </c>
-      <c r="AEE23" s="7">
-        <v>770352</v>
-      </c>
-      <c r="AEF23" s="7">
-        <v>706384</v>
-      </c>
-      <c r="AEG23" s="7">
-        <v>603944</v>
-      </c>
-      <c r="AEH23" s="7">
-        <v>590538</v>
-      </c>
-      <c r="AEI23" s="7">
-        <v>566310</v>
-      </c>
-      <c r="AEJ23" s="7">
-        <v>514390</v>
-      </c>
-      <c r="AEK23" s="7">
-        <v>458581</v>
-      </c>
-      <c r="AEL23" s="7">
-        <v>438797</v>
-      </c>
-      <c r="AEM23" s="7">
-        <v>439363</v>
-      </c>
-      <c r="AEN23" s="7">
-        <v>425721</v>
-      </c>
-      <c r="AEO23" s="7">
-        <v>403271</v>
-      </c>
-      <c r="AEP23" s="7">
-        <v>377245</v>
-      </c>
-      <c r="AEQ23" s="7">
-        <v>351611</v>
-      </c>
-      <c r="AER23" s="7">
-        <v>322528</v>
-      </c>
-      <c r="AES23" s="7">
-        <v>294994</v>
-      </c>
-      <c r="AET23" s="7">
-        <v>274558</v>
-      </c>
-      <c r="AEU23" s="7">
-        <v>253991</v>
-      </c>
-      <c r="AEV23" s="7">
-        <v>229189</v>
-      </c>
-      <c r="AEW23" s="7">
-        <v>200654</v>
-      </c>
-      <c r="AEX23" s="7">
-        <v>171901</v>
-      </c>
-      <c r="AEY23" s="7">
-        <v>147173</v>
-      </c>
-      <c r="AEZ23" s="7">
-        <v>126926</v>
-      </c>
-      <c r="AFA23" s="7">
-        <v>105853</v>
-      </c>
-      <c r="AFB23" s="7">
-        <v>87009</v>
-      </c>
-      <c r="AFC23" s="7">
-        <v>70673</v>
-      </c>
-      <c r="AFD23" s="7">
-        <v>56966</v>
-      </c>
-      <c r="AFE23" s="7">
-        <v>44496</v>
-      </c>
-      <c r="AFF23" s="7">
-        <v>31169</v>
-      </c>
-      <c r="AFG23" s="7">
-        <v>18270</v>
-      </c>
-      <c r="AFH23" s="7">
-        <v>11405</v>
-      </c>
-      <c r="AFI23" s="7">
-        <v>8115</v>
-      </c>
-      <c r="AFJ23" s="7">
-        <v>681496</v>
-      </c>
-      <c r="AFK23" s="7">
-        <v>671931</v>
-      </c>
-      <c r="AFL23" s="7">
-        <v>678611</v>
-      </c>
-      <c r="AFM23" s="7">
-        <v>691186</v>
-      </c>
-      <c r="AFN23" s="7">
-        <v>714964</v>
-      </c>
-      <c r="AFO23" s="7">
-        <v>759835</v>
-      </c>
-      <c r="AFP23" s="7">
-        <v>695538</v>
-      </c>
-      <c r="AFQ23" s="7">
-        <v>593498</v>
-      </c>
-      <c r="AFR23" s="7">
-        <v>579303</v>
-      </c>
-      <c r="AFS23" s="7">
-        <v>554398</v>
-      </c>
-      <c r="AFT23" s="7">
-        <v>502282</v>
-      </c>
-      <c r="AFU23" s="7">
-        <v>446735</v>
-      </c>
-      <c r="AFV23" s="7">
-        <v>426008</v>
-      </c>
-      <c r="AFW23" s="7">
-        <v>424992</v>
-      </c>
-      <c r="AFX23" s="7">
-        <v>410099</v>
-      </c>
-      <c r="AFY23" s="7">
-        <v>386720</v>
-      </c>
-      <c r="AFZ23" s="7">
-        <v>359691</v>
-      </c>
-      <c r="AGA23" s="7">
-        <v>333081</v>
-      </c>
-      <c r="AGB23" s="7">
-        <v>303355</v>
-      </c>
-      <c r="AGC23" s="7">
-        <v>274958</v>
-      </c>
-      <c r="AGD23" s="7">
-        <v>253461</v>
-      </c>
-      <c r="AGE23" s="7">
-        <v>232125</v>
-      </c>
-      <c r="AGF23" s="7">
-        <v>206654</v>
-      </c>
-      <c r="AGG23" s="7">
-        <v>178698</v>
-      </c>
-      <c r="AGH23" s="7">
-        <v>150565</v>
-      </c>
-      <c r="AGI23" s="7">
-        <v>127124</v>
-      </c>
-      <c r="AGJ23" s="7">
-        <v>106500</v>
-      </c>
-      <c r="AGK23" s="7">
-        <v>87132</v>
-      </c>
-      <c r="AGL23" s="7">
-        <v>70219</v>
-      </c>
-      <c r="AGM23" s="7">
-        <v>55865</v>
-      </c>
-      <c r="AGN23" s="7">
-        <v>43875</v>
-      </c>
-      <c r="AGO23" s="7">
-        <v>33235</v>
-      </c>
-      <c r="AGP23" s="7">
-        <v>22628</v>
-      </c>
-      <c r="AGQ23" s="7">
-        <v>12940</v>
-      </c>
-      <c r="AGR23" s="7">
-        <v>7896</v>
-      </c>
-      <c r="AGS23" s="7">
-        <v>691991</v>
-      </c>
-      <c r="AGT23" s="7">
-        <v>674743</v>
-      </c>
-      <c r="AGU23" s="7">
-        <v>664653</v>
-      </c>
-      <c r="AGV23" s="7">
-        <v>670718</v>
-      </c>
-      <c r="AGW23" s="7">
-        <v>682427</v>
-      </c>
-      <c r="AGX23" s="7">
-        <v>705113</v>
-      </c>
-      <c r="AGY23" s="7">
-        <v>748303</v>
-      </c>
-      <c r="AGZ23" s="7">
-        <v>683871</v>
-      </c>
-      <c r="AHA23" s="7">
-        <v>582242</v>
-      </c>
-      <c r="AHB23" s="7">
-        <v>566860</v>
-      </c>
-      <c r="AHC23" s="7">
-        <v>540884</v>
-      </c>
-      <c r="AHD23" s="7">
-        <v>488473</v>
-      </c>
-      <c r="AHE23" s="7">
-        <v>432690</v>
-      </c>
-      <c r="AHF23" s="7">
-        <v>410990</v>
-      </c>
-      <c r="AHG23" s="7">
-        <v>408464</v>
-      </c>
-      <c r="AHH23" s="7">
-        <v>392245</v>
-      </c>
-      <c r="AHI23" s="7">
-        <v>367804</v>
-      </c>
-      <c r="AHJ23" s="7">
-        <v>340044</v>
-      </c>
-      <c r="AHK23" s="7">
-        <v>312735</v>
-      </c>
-      <c r="AHL23" s="7">
-        <v>282309</v>
-      </c>
-      <c r="AHM23" s="7">
-        <v>253450</v>
-      </c>
-      <c r="AHN23" s="7">
-        <v>231065</v>
-      </c>
-      <c r="AHO23" s="7">
-        <v>208867</v>
-      </c>
-      <c r="AHP23" s="7">
-        <v>183526</v>
-      </c>
-      <c r="AHQ23" s="7">
-        <v>156038</v>
-      </c>
-      <c r="AHR23" s="7">
-        <v>129184</v>
-      </c>
-      <c r="AHS23" s="7">
-        <v>108780</v>
-      </c>
-      <c r="AHT23" s="7">
-        <v>89481</v>
-      </c>
-      <c r="AHU23" s="7">
-        <v>71029</v>
-      </c>
-      <c r="AHV23" s="7">
-        <v>55705</v>
-      </c>
-      <c r="AHW23" s="7">
-        <v>42677</v>
-      </c>
-      <c r="AHX23" s="7">
-        <v>32368</v>
-      </c>
-      <c r="AHY23" s="7">
-        <v>24181</v>
-      </c>
-      <c r="AHZ23" s="7">
-        <v>17403</v>
-      </c>
-      <c r="AIA23" s="7">
-        <v>7743</v>
-      </c>
-      <c r="AIB23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AIC23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AID23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AIE23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AIF23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AIG23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AIH23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AII23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AIJ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AIK23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AIL23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AIM23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AIN23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AIO23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AIP23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AIQ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AIR23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AIS23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AIT23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AIU23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AIV23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AIW23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AIX23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AIY23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AIZ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJA23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJB23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJC23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJD23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJE23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJF23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJG23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJH23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJI23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJJ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJK23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJL23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJM23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJN23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJO23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJP23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJQ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJR23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJS23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJT23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJU23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJV23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJW23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJX23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJY23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJZ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKA23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKB23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKC23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKD23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKE23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKF23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKG23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKH23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKI23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKJ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKK23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKL23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKM23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKN23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKO23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKP23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKQ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKR23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKS23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKT23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKU23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKV23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKW23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKX23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKY23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AKZ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALA23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALB23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALC23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALD23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALE23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALF23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALG23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALH23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALI23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALJ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALK23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALL23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALM23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALN23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALO23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALP23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALQ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALR23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALS23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALT23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALU23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALV23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALW23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALX23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALY23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ALZ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AMA23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AMB23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AMC23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AMD23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AME23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AMF23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AMG23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AMH23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AMI23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AMJ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AMK23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AML23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AMM23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AMN23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AMO23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AMP23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AMQ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AMR23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AMS23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AMT23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AMU23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AMV23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AMW23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AMX23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AMY23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AMZ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANA23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANB23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANC23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AND23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANE23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANF23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANG23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANH23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANI23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANJ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANK23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANL23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANM23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANN23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANO23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANP23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANQ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANR23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANS23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANT23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANU23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANV23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANW23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANX23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANY23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="ANZ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AOA23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AOB23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AOC23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AOD23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AOE23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AOF23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AOG23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AOH23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AOI23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AOJ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AOK23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AOL23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AOM23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AON23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AOO23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AOP23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AOQ23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AOR23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AOS23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="AOT23" s="7" t="s">
-        <v>72</v>
+      <c r="MN23" s="10">
+        <v>86863</v>
+      </c>
+      <c r="MO23" s="10">
+        <v>82140</v>
+      </c>
+      <c r="MP23" s="10">
+        <v>79198</v>
+      </c>
+      <c r="MQ23" s="10">
+        <v>75074</v>
+      </c>
+      <c r="MR23" s="10">
+        <v>72402</v>
+      </c>
+      <c r="MS23" s="10">
+        <v>70149</v>
+      </c>
+      <c r="MT23" s="10">
+        <v>71881</v>
+      </c>
+      <c r="MU23" s="10">
+        <v>70591</v>
+      </c>
+      <c r="MV23" s="10">
+        <v>70644</v>
+      </c>
+      <c r="MW23" s="10">
+        <v>67132</v>
+      </c>
+      <c r="MX23" s="10">
+        <v>67807</v>
+      </c>
+      <c r="MY23" s="10">
+        <v>64345</v>
+      </c>
+      <c r="MZ23" s="10">
+        <v>63666</v>
+      </c>
+      <c r="NA23" s="10">
+        <v>62912</v>
+      </c>
+      <c r="NB23" s="10">
+        <v>60512</v>
+      </c>
+      <c r="NC23" s="10">
+        <v>58581</v>
+      </c>
+      <c r="ND23" s="10">
+        <v>55117</v>
+      </c>
+      <c r="NE23" s="10">
+        <v>55363</v>
+      </c>
+      <c r="NF23" s="10">
+        <v>53694</v>
+      </c>
+      <c r="NG23" s="10">
+        <v>40438</v>
+      </c>
+      <c r="NH23" s="10">
+        <v>36271</v>
+      </c>
+      <c r="NI23" s="10">
+        <v>32715</v>
+      </c>
+      <c r="NJ23" s="10">
+        <v>28297</v>
+      </c>
+      <c r="NK23" s="10">
+        <v>23947</v>
+      </c>
+      <c r="NL23" s="10">
+        <v>21001</v>
+      </c>
+      <c r="NM23" s="10">
+        <v>17438</v>
+      </c>
+      <c r="NN23" s="10">
+        <v>14244</v>
+      </c>
+      <c r="NO23" s="10">
+        <v>10961</v>
+      </c>
+      <c r="NP23" s="10">
+        <v>8379</v>
+      </c>
+      <c r="NQ23" s="10">
+        <v>6400</v>
+      </c>
+      <c r="NR23" s="10">
+        <v>4482</v>
+      </c>
+      <c r="NS23" s="10">
+        <v>3144</v>
+      </c>
+      <c r="NT23" s="10">
+        <v>2108</v>
+      </c>
+      <c r="NU23" s="10">
+        <v>1319</v>
+      </c>
+      <c r="NV23" s="10">
+        <v>839</v>
+      </c>
+      <c r="NW23" s="10">
+        <v>90241</v>
+      </c>
+      <c r="NX23" s="10">
+        <v>85877</v>
+      </c>
+      <c r="NY23" s="10">
+        <v>81117</v>
+      </c>
+      <c r="NZ23" s="10">
+        <v>78125</v>
+      </c>
+      <c r="OA23" s="10">
+        <v>73888</v>
+      </c>
+      <c r="OB23" s="10">
+        <v>71193</v>
+      </c>
+      <c r="OC23" s="10">
+        <v>68795</v>
+      </c>
+      <c r="OD23" s="10">
+        <v>70363</v>
+      </c>
+      <c r="OE23" s="10">
+        <v>69016</v>
+      </c>
+      <c r="OF23" s="10">
+        <v>68826</v>
+      </c>
+      <c r="OG23" s="10">
+        <v>65259</v>
+      </c>
+      <c r="OH23" s="10">
+        <v>65780</v>
+      </c>
+      <c r="OI23" s="10">
+        <v>62086</v>
+      </c>
+      <c r="OJ23" s="10">
+        <v>61236</v>
+      </c>
+      <c r="OK23" s="10">
+        <v>60196</v>
+      </c>
+      <c r="OL23" s="10">
+        <v>57632</v>
+      </c>
+      <c r="OM23" s="10">
+        <v>55350</v>
+      </c>
+      <c r="ON23" s="10">
+        <v>51691</v>
+      </c>
+      <c r="OO23" s="10">
+        <v>51546</v>
+      </c>
+      <c r="OP23" s="10">
+        <v>49463</v>
+      </c>
+      <c r="OQ23" s="10">
+        <v>36903</v>
+      </c>
+      <c r="OR23" s="10">
+        <v>32560</v>
+      </c>
+      <c r="OS23" s="10">
+        <v>29075</v>
+      </c>
+      <c r="OT23" s="10">
+        <v>24722</v>
+      </c>
+      <c r="OU23" s="10">
+        <v>20553</v>
+      </c>
+      <c r="OV23" s="10">
+        <v>17712</v>
+      </c>
+      <c r="OW23" s="10">
+        <v>14459</v>
+      </c>
+      <c r="OX23" s="10">
+        <v>11588</v>
+      </c>
+      <c r="OY23" s="10">
+        <v>8705</v>
+      </c>
+      <c r="OZ23" s="10">
+        <v>6470</v>
+      </c>
+      <c r="PA23" s="10">
+        <v>4794</v>
+      </c>
+      <c r="PB23" s="10">
+        <v>3278</v>
+      </c>
+      <c r="PC23" s="10">
+        <v>2227</v>
+      </c>
+      <c r="PD23" s="10">
+        <v>1456</v>
+      </c>
+      <c r="PE23" s="10">
+        <v>875</v>
+      </c>
+      <c r="PF23" s="10">
+        <v>89319</v>
+      </c>
+      <c r="PG23" s="10">
+        <v>89192</v>
+      </c>
+      <c r="PH23" s="10">
+        <v>84742</v>
+      </c>
+      <c r="PI23" s="10">
+        <v>80017</v>
+      </c>
+      <c r="PJ23" s="10">
+        <v>76991</v>
+      </c>
+      <c r="PK23" s="10">
+        <v>72627</v>
+      </c>
+      <c r="PL23" s="10">
+        <v>69903</v>
+      </c>
+      <c r="PM23" s="10">
+        <v>67452</v>
+      </c>
+      <c r="PN23" s="10">
+        <v>68803</v>
+      </c>
+      <c r="PO23" s="10">
+        <v>67230</v>
+      </c>
+      <c r="PP23" s="10">
+        <v>66855</v>
+      </c>
+      <c r="PQ23" s="10">
+        <v>63338</v>
+      </c>
+      <c r="PR23" s="10">
+        <v>63480</v>
+      </c>
+      <c r="PS23" s="10">
+        <v>59721</v>
+      </c>
+      <c r="PT23" s="10">
+        <v>58544</v>
+      </c>
+      <c r="PU23" s="10">
+        <v>57215</v>
+      </c>
+      <c r="PV23" s="10">
+        <v>54454</v>
+      </c>
+      <c r="PW23" s="10">
+        <v>51994</v>
+      </c>
+      <c r="PX23" s="10">
+        <v>47964</v>
+      </c>
+      <c r="PY23" s="10">
+        <v>47594</v>
+      </c>
+      <c r="PZ23" s="10">
+        <v>45059</v>
+      </c>
+      <c r="QA23" s="10">
+        <v>33284</v>
+      </c>
+      <c r="QB23" s="10">
+        <v>28865</v>
+      </c>
+      <c r="QC23" s="10">
+        <v>25400</v>
+      </c>
+      <c r="QD23" s="10">
+        <v>21268</v>
+      </c>
+      <c r="QE23" s="10">
+        <v>17327</v>
+      </c>
+      <c r="QF23" s="10">
+        <v>14680</v>
+      </c>
+      <c r="QG23" s="10">
+        <v>11718</v>
+      </c>
+      <c r="QH23" s="10">
+        <v>9098</v>
+      </c>
+      <c r="QI23" s="10">
+        <v>6689</v>
+      </c>
+      <c r="QJ23" s="10">
+        <v>4861</v>
+      </c>
+      <c r="QK23" s="10">
+        <v>3521</v>
+      </c>
+      <c r="QL23" s="10">
+        <v>2345</v>
+      </c>
+      <c r="QM23" s="10">
+        <v>1519</v>
+      </c>
+      <c r="QN23" s="10">
+        <v>966</v>
+      </c>
+      <c r="QO23" s="10">
+        <v>93339</v>
+      </c>
+      <c r="QP23" s="10">
+        <v>88347</v>
+      </c>
+      <c r="QQ23" s="10">
+        <v>88224</v>
+      </c>
+      <c r="QR23" s="10">
+        <v>83695</v>
+      </c>
+      <c r="QS23" s="10">
+        <v>78949</v>
+      </c>
+      <c r="QT23" s="10">
+        <v>75771</v>
+      </c>
+      <c r="QU23" s="10">
+        <v>71364</v>
+      </c>
+      <c r="QV23" s="10">
+        <v>68460</v>
+      </c>
+      <c r="QW23" s="10">
+        <v>66032</v>
+      </c>
+      <c r="QX23" s="10">
+        <v>67167</v>
+      </c>
+      <c r="QY23" s="10">
+        <v>65421</v>
+      </c>
+      <c r="QZ23" s="10">
+        <v>64921</v>
+      </c>
+      <c r="RA23" s="10">
+        <v>61210</v>
+      </c>
+      <c r="RB23" s="10">
+        <v>61093</v>
+      </c>
+      <c r="RC23" s="10">
+        <v>57190</v>
+      </c>
+      <c r="RD23" s="10">
+        <v>55811</v>
+      </c>
+      <c r="RE23" s="10">
+        <v>54132</v>
+      </c>
+      <c r="RF23" s="10">
+        <v>51161</v>
+      </c>
+      <c r="RG23" s="10">
+        <v>48517</v>
+      </c>
+      <c r="RH23" s="10">
+        <v>44190</v>
+      </c>
+      <c r="RI23" s="10">
+        <v>43398</v>
+      </c>
+      <c r="RJ23" s="10">
+        <v>40609</v>
+      </c>
+      <c r="RK23" s="10">
+        <v>29729</v>
+      </c>
+      <c r="RL23" s="10">
+        <v>25281</v>
+      </c>
+      <c r="RM23" s="10">
+        <v>21829</v>
+      </c>
+      <c r="RN23" s="10">
+        <v>17993</v>
+      </c>
+      <c r="RO23" s="10">
+        <v>14372</v>
+      </c>
+      <c r="RP23" s="10">
+        <v>11853</v>
+      </c>
+      <c r="RQ23" s="10">
+        <v>9273</v>
+      </c>
+      <c r="RR23" s="10">
+        <v>7098</v>
+      </c>
+      <c r="RS23" s="10">
+        <v>4985</v>
+      </c>
+      <c r="RT23" s="10">
+        <v>3524</v>
+      </c>
+      <c r="RU23" s="10">
+        <v>2475</v>
+      </c>
+      <c r="RV23" s="10">
+        <v>1634</v>
+      </c>
+      <c r="RW23" s="10">
+        <v>983</v>
+      </c>
+      <c r="RX23" s="10">
+        <v>105147</v>
+      </c>
+      <c r="RY23" s="10">
+        <v>92288</v>
+      </c>
+      <c r="RZ23" s="10">
+        <v>87351</v>
+      </c>
+      <c r="SA23" s="10">
+        <v>87089</v>
+      </c>
+      <c r="SB23" s="10">
+        <v>82611</v>
+      </c>
+      <c r="SC23" s="10">
+        <v>77707</v>
+      </c>
+      <c r="SD23" s="10">
+        <v>74553</v>
+      </c>
+      <c r="SE23" s="10">
+        <v>70042</v>
+      </c>
+      <c r="SF23" s="10">
+        <v>66978</v>
+      </c>
+      <c r="SG23" s="10">
+        <v>64554</v>
+      </c>
+      <c r="SH23" s="10">
+        <v>65438</v>
+      </c>
+      <c r="SI23" s="10">
+        <v>63453</v>
+      </c>
+      <c r="SJ23" s="10">
+        <v>62808</v>
+      </c>
+      <c r="SK23" s="10">
+        <v>58863</v>
+      </c>
+      <c r="SL23" s="10">
+        <v>58569</v>
+      </c>
+      <c r="SM23" s="10">
+        <v>54474</v>
+      </c>
+      <c r="SN23" s="10">
+        <v>52806</v>
+      </c>
+      <c r="SO23" s="10">
+        <v>50845</v>
+      </c>
+      <c r="SP23" s="10">
+        <v>47641</v>
+      </c>
+      <c r="SQ23" s="10">
+        <v>44904</v>
+      </c>
+      <c r="SR23" s="10">
+        <v>40296</v>
+      </c>
+      <c r="SS23" s="10">
+        <v>39193</v>
+      </c>
+      <c r="ST23" s="10">
+        <v>36118</v>
+      </c>
+      <c r="SU23" s="10">
+        <v>26053</v>
+      </c>
+      <c r="SV23" s="10">
+        <v>21704</v>
+      </c>
+      <c r="SW23" s="10">
+        <v>18449</v>
+      </c>
+      <c r="SX23" s="10">
+        <v>14915</v>
+      </c>
+      <c r="SY23" s="10">
+        <v>11652</v>
+      </c>
+      <c r="SZ23" s="10">
+        <v>9289</v>
+      </c>
+      <c r="TA23" s="10">
+        <v>7061</v>
+      </c>
+      <c r="TB23" s="10">
+        <v>5306</v>
+      </c>
+      <c r="TC23" s="10">
+        <v>3564</v>
+      </c>
+      <c r="TD23" s="10">
+        <v>2489</v>
+      </c>
+      <c r="TE23" s="10">
+        <v>1655</v>
+      </c>
+      <c r="TF23" s="10">
+        <v>1090</v>
+      </c>
+      <c r="TG23" s="10">
+        <v>114389</v>
+      </c>
+      <c r="TH23" s="10">
+        <v>104072</v>
+      </c>
+      <c r="TI23" s="10">
+        <v>91217</v>
+      </c>
+      <c r="TJ23" s="10">
+        <v>86332</v>
+      </c>
+      <c r="TK23" s="10">
+        <v>85811</v>
+      </c>
+      <c r="TL23" s="10">
+        <v>81385</v>
+      </c>
+      <c r="TM23" s="10">
+        <v>76448</v>
+      </c>
+      <c r="TN23" s="10">
+        <v>73193</v>
+      </c>
+      <c r="TO23" s="10">
+        <v>68667</v>
+      </c>
+      <c r="TP23" s="10">
+        <v>65419</v>
+      </c>
+      <c r="TQ23" s="10">
+        <v>62888</v>
+      </c>
+      <c r="TR23" s="10">
+        <v>63609</v>
+      </c>
+      <c r="TS23" s="10">
+        <v>61451</v>
+      </c>
+      <c r="TT23" s="10">
+        <v>60538</v>
+      </c>
+      <c r="TU23" s="10">
+        <v>56549</v>
+      </c>
+      <c r="TV23" s="10">
+        <v>55907</v>
+      </c>
+      <c r="TW23" s="10">
+        <v>51528</v>
+      </c>
+      <c r="TX23" s="10">
+        <v>49729</v>
+      </c>
+      <c r="TY23" s="10">
+        <v>47387</v>
+      </c>
+      <c r="TZ23" s="10">
+        <v>44053</v>
+      </c>
+      <c r="UA23" s="10">
+        <v>41085</v>
+      </c>
+      <c r="UB23" s="10">
+        <v>36353</v>
+      </c>
+      <c r="UC23" s="10">
+        <v>34942</v>
+      </c>
+      <c r="UD23" s="10">
+        <v>31666</v>
+      </c>
+      <c r="UE23" s="10">
+        <v>22491</v>
+      </c>
+      <c r="UF23" s="10">
+        <v>18266</v>
+      </c>
+      <c r="UG23" s="10">
+        <v>15285</v>
+      </c>
+      <c r="UH23" s="10">
+        <v>12048</v>
+      </c>
+      <c r="UI23" s="10">
+        <v>9158</v>
+      </c>
+      <c r="UJ23" s="10">
+        <v>7185</v>
+      </c>
+      <c r="UK23" s="10">
+        <v>5350</v>
+      </c>
+      <c r="UL23" s="10">
+        <v>3816</v>
+      </c>
+      <c r="UM23" s="10">
+        <v>2535</v>
+      </c>
+      <c r="UN23" s="10">
+        <v>1692</v>
+      </c>
+      <c r="UO23" s="10">
+        <v>1092</v>
+      </c>
+      <c r="UP23" s="10">
+        <v>121996</v>
+      </c>
+      <c r="UQ23" s="10">
+        <v>113294</v>
+      </c>
+      <c r="UR23" s="10">
+        <v>103011</v>
+      </c>
+      <c r="US23" s="10">
+        <v>90193</v>
+      </c>
+      <c r="UT23" s="10">
+        <v>85263</v>
+      </c>
+      <c r="UU23" s="10">
+        <v>84557</v>
+      </c>
+      <c r="UV23" s="10">
+        <v>80133</v>
+      </c>
+      <c r="UW23" s="10">
+        <v>75096</v>
+      </c>
+      <c r="UX23" s="10">
+        <v>71680</v>
+      </c>
+      <c r="UY23" s="10">
+        <v>67108</v>
+      </c>
+      <c r="UZ23" s="10">
+        <v>63750</v>
+      </c>
+      <c r="VA23" s="10">
+        <v>61169</v>
+      </c>
+      <c r="VB23" s="10">
+        <v>61652</v>
+      </c>
+      <c r="VC23" s="10">
+        <v>59306</v>
+      </c>
+      <c r="VD23" s="10">
+        <v>58184</v>
+      </c>
+      <c r="VE23" s="10">
+        <v>53981</v>
+      </c>
+      <c r="VF23" s="10">
+        <v>53105</v>
+      </c>
+      <c r="VG23" s="10">
+        <v>48617</v>
+      </c>
+      <c r="VH23" s="10">
+        <v>46603</v>
+      </c>
+      <c r="VI23" s="10">
+        <v>43903</v>
+      </c>
+      <c r="VJ23" s="10">
+        <v>40365</v>
+      </c>
+      <c r="VK23" s="10">
+        <v>37203</v>
+      </c>
+      <c r="VL23" s="10">
+        <v>32502</v>
+      </c>
+      <c r="VM23" s="10">
+        <v>30753</v>
+      </c>
+      <c r="VN23" s="10">
+        <v>27372</v>
+      </c>
+      <c r="VO23" s="10">
+        <v>19120</v>
+      </c>
+      <c r="VP23" s="10">
+        <v>15292</v>
+      </c>
+      <c r="VQ23" s="10">
+        <v>12499</v>
+      </c>
+      <c r="VR23" s="10">
+        <v>9547</v>
+      </c>
+      <c r="VS23" s="10">
+        <v>6993</v>
+      </c>
+      <c r="VT23" s="10">
+        <v>5417</v>
+      </c>
+      <c r="VU23" s="10">
+        <v>3936</v>
+      </c>
+      <c r="VV23" s="10">
+        <v>2722</v>
+      </c>
+      <c r="VW23" s="10">
+        <v>1732</v>
+      </c>
+      <c r="VX23" s="10">
+        <v>1087</v>
+      </c>
+      <c r="VY23" s="10">
+        <v>123950</v>
+      </c>
+      <c r="VZ23" s="10">
+        <v>120794</v>
+      </c>
+      <c r="WA23" s="10">
+        <v>112085</v>
+      </c>
+      <c r="WB23" s="10">
+        <v>101818</v>
+      </c>
+      <c r="WC23" s="10">
+        <v>89038</v>
+      </c>
+      <c r="WD23" s="10">
+        <v>83971</v>
+      </c>
+      <c r="WE23" s="10">
+        <v>83221</v>
+      </c>
+      <c r="WF23" s="10">
+        <v>78742</v>
+      </c>
+      <c r="WG23" s="10">
+        <v>73610</v>
+      </c>
+      <c r="WH23" s="10">
+        <v>70071</v>
+      </c>
+      <c r="WI23" s="10">
+        <v>65447</v>
+      </c>
+      <c r="WJ23" s="10">
+        <v>61982</v>
+      </c>
+      <c r="WK23" s="10">
+        <v>59287</v>
+      </c>
+      <c r="WL23" s="10">
+        <v>59438</v>
+      </c>
+      <c r="WM23" s="10">
+        <v>56888</v>
+      </c>
+      <c r="WN23" s="10">
+        <v>55651</v>
+      </c>
+      <c r="WO23" s="10">
+        <v>51235</v>
+      </c>
+      <c r="WP23" s="10">
+        <v>50088</v>
+      </c>
+      <c r="WQ23" s="10">
+        <v>45476</v>
+      </c>
+      <c r="WR23" s="10">
+        <v>43237</v>
+      </c>
+      <c r="WS23" s="10">
+        <v>40351</v>
+      </c>
+      <c r="WT23" s="10">
+        <v>36588</v>
+      </c>
+      <c r="WU23" s="10">
+        <v>33288</v>
+      </c>
+      <c r="WV23" s="10">
+        <v>28598</v>
+      </c>
+      <c r="WW23" s="10">
+        <v>26649</v>
+      </c>
+      <c r="WX23" s="10">
+        <v>23310</v>
+      </c>
+      <c r="WY23" s="10">
+        <v>15848</v>
+      </c>
+      <c r="WZ23" s="10">
+        <v>12447</v>
+      </c>
+      <c r="XA23" s="10">
+        <v>9965</v>
+      </c>
+      <c r="XB23" s="10">
+        <v>7342</v>
+      </c>
+      <c r="XC23" s="10">
+        <v>5276</v>
+      </c>
+      <c r="XD23" s="10">
+        <v>4000</v>
+      </c>
+      <c r="XE23" s="10">
+        <v>2816</v>
+      </c>
+      <c r="XF23" s="10">
+        <v>1905</v>
+      </c>
+      <c r="XG23" s="10">
+        <v>1175</v>
+      </c>
+      <c r="XH23" s="10">
+        <v>124876</v>
+      </c>
+      <c r="XI23" s="10">
+        <v>122744</v>
+      </c>
+      <c r="XJ23" s="10">
+        <v>119515</v>
+      </c>
+      <c r="XK23" s="10">
+        <v>110835</v>
+      </c>
+      <c r="XL23" s="10">
+        <v>100493</v>
+      </c>
+      <c r="XM23" s="10">
+        <v>87771</v>
+      </c>
+      <c r="XN23" s="10">
+        <v>82656</v>
+      </c>
+      <c r="XO23" s="10">
+        <v>81757</v>
+      </c>
+      <c r="XP23" s="10">
+        <v>77224</v>
+      </c>
+      <c r="XQ23" s="10">
+        <v>72024</v>
+      </c>
+      <c r="XR23" s="10">
+        <v>68465</v>
+      </c>
+      <c r="XS23" s="10">
+        <v>63635</v>
+      </c>
+      <c r="XT23" s="10">
+        <v>60057</v>
+      </c>
+      <c r="XU23" s="10">
+        <v>57266</v>
+      </c>
+      <c r="XV23" s="10">
+        <v>57132</v>
+      </c>
+      <c r="XW23" s="10">
+        <v>54407</v>
+      </c>
+      <c r="XX23" s="10">
+        <v>52992</v>
+      </c>
+      <c r="XY23" s="10">
+        <v>48318</v>
+      </c>
+      <c r="XZ23" s="10">
+        <v>46936</v>
+      </c>
+      <c r="YA23" s="10">
+        <v>42238</v>
+      </c>
+      <c r="YB23" s="10">
+        <v>39673</v>
+      </c>
+      <c r="YC23" s="10">
+        <v>36671</v>
+      </c>
+      <c r="YD23" s="10">
+        <v>32788</v>
+      </c>
+      <c r="YE23" s="10">
+        <v>29336</v>
+      </c>
+      <c r="YF23" s="10">
+        <v>24849</v>
+      </c>
+      <c r="YG23" s="10">
+        <v>22744</v>
+      </c>
+      <c r="YH23" s="10">
+        <v>19464</v>
+      </c>
+      <c r="YI23" s="10">
+        <v>12916</v>
+      </c>
+      <c r="YJ23" s="10">
+        <v>9880</v>
+      </c>
+      <c r="YK23" s="10">
+        <v>7754</v>
+      </c>
+      <c r="YL23" s="10">
+        <v>5526</v>
+      </c>
+      <c r="YM23" s="10">
+        <v>3845</v>
+      </c>
+      <c r="YN23" s="10">
+        <v>2892</v>
+      </c>
+      <c r="YO23" s="10">
+        <v>1939</v>
+      </c>
+      <c r="YP23" s="10">
+        <v>1280</v>
+      </c>
+      <c r="YQ23" s="10">
+        <v>123226</v>
+      </c>
+      <c r="YR23" s="10">
+        <v>123668</v>
+      </c>
+      <c r="YS23" s="10">
+        <v>121512</v>
+      </c>
+      <c r="YT23" s="10">
+        <v>118171</v>
+      </c>
+      <c r="YU23" s="10">
+        <v>109354</v>
+      </c>
+      <c r="YV23" s="10">
+        <v>99169</v>
+      </c>
+      <c r="YW23" s="10">
+        <v>86438</v>
+      </c>
+      <c r="YX23" s="10">
+        <v>81285</v>
+      </c>
+      <c r="YY23" s="10">
+        <v>80145</v>
+      </c>
+      <c r="YZ23" s="10">
+        <v>75556</v>
+      </c>
+      <c r="ZA23" s="10">
+        <v>70267</v>
+      </c>
+      <c r="ZB23" s="10">
+        <v>66606</v>
+      </c>
+      <c r="ZC23" s="10">
+        <v>61725</v>
+      </c>
+      <c r="ZD23" s="10">
+        <v>57911</v>
+      </c>
+      <c r="ZE23" s="10">
+        <v>55102</v>
+      </c>
+      <c r="ZF23" s="10">
+        <v>54609</v>
+      </c>
+      <c r="ZG23" s="10">
+        <v>51703</v>
+      </c>
+      <c r="ZH23" s="10">
+        <v>50073</v>
+      </c>
+      <c r="ZI23" s="10">
+        <v>45210</v>
+      </c>
+      <c r="ZJ23" s="10">
+        <v>43585</v>
+      </c>
+      <c r="ZK23" s="10">
+        <v>38763</v>
+      </c>
+      <c r="ZL23" s="10">
+        <v>35969</v>
+      </c>
+      <c r="ZM23" s="10">
+        <v>32799</v>
+      </c>
+      <c r="ZN23" s="10">
+        <v>28890</v>
+      </c>
+      <c r="ZO23" s="10">
+        <v>25315</v>
+      </c>
+      <c r="ZP23" s="10">
+        <v>21024</v>
+      </c>
+      <c r="ZQ23" s="10">
+        <v>18973</v>
+      </c>
+      <c r="ZR23" s="10">
+        <v>15878</v>
+      </c>
+      <c r="ZS23" s="10">
+        <v>10256</v>
+      </c>
+      <c r="ZT23" s="10">
+        <v>7544</v>
+      </c>
+      <c r="ZU23" s="10">
+        <v>5779</v>
+      </c>
+      <c r="ZV23" s="10">
+        <v>4008</v>
+      </c>
+      <c r="ZW23" s="10">
+        <v>2685</v>
+      </c>
+      <c r="ZX23" s="10">
+        <v>1968</v>
+      </c>
+      <c r="ZY23" s="10">
+        <v>1281</v>
+      </c>
+      <c r="ZZ23" s="10">
+        <v>121945</v>
+      </c>
+      <c r="AAA23" s="10">
+        <v>122064</v>
+      </c>
+      <c r="AAB23" s="10">
+        <v>122449</v>
+      </c>
+      <c r="AAC23" s="10">
+        <v>120131</v>
+      </c>
+      <c r="AAD23" s="10">
+        <v>116767</v>
+      </c>
+      <c r="AAE23" s="10">
+        <v>107858</v>
+      </c>
+      <c r="AAF23" s="10">
+        <v>97649</v>
+      </c>
+      <c r="AAG23" s="10">
+        <v>85029</v>
+      </c>
+      <c r="AAH23" s="10">
+        <v>79797</v>
+      </c>
+      <c r="AAI23" s="10">
+        <v>78497</v>
+      </c>
+      <c r="AAJ23" s="10">
+        <v>73736</v>
+      </c>
+      <c r="AAK23" s="10">
+        <v>68405</v>
+      </c>
+      <c r="AAL23" s="10">
+        <v>64634</v>
+      </c>
+      <c r="AAM23" s="10">
+        <v>59719</v>
+      </c>
+      <c r="AAN23" s="10">
+        <v>55810</v>
+      </c>
+      <c r="AAO23" s="10">
+        <v>52721</v>
+      </c>
+      <c r="AAP23" s="10">
+        <v>51954</v>
+      </c>
+      <c r="AAQ23" s="10">
+        <v>48943</v>
+      </c>
+      <c r="AAR23" s="10">
+        <v>47027</v>
+      </c>
+      <c r="AAS23" s="10">
+        <v>42043</v>
+      </c>
+      <c r="AAT23" s="10">
+        <v>40125</v>
+      </c>
+      <c r="AAU23" s="10">
+        <v>35319</v>
+      </c>
+      <c r="AAV23" s="10">
+        <v>32394</v>
+      </c>
+      <c r="AAW23" s="10">
+        <v>29097</v>
+      </c>
+      <c r="AAX23" s="10">
+        <v>25079</v>
+      </c>
+      <c r="AAY23" s="10">
+        <v>21604</v>
+      </c>
+      <c r="AAZ23" s="10">
+        <v>17571</v>
+      </c>
+      <c r="ABA23" s="10">
+        <v>15371</v>
+      </c>
+      <c r="ABB23" s="10">
+        <v>12725</v>
+      </c>
+      <c r="ABC23" s="10">
+        <v>7985</v>
+      </c>
+      <c r="ABD23" s="10">
+        <v>5716</v>
+      </c>
+      <c r="ABE23" s="10">
+        <v>4222</v>
+      </c>
+      <c r="ABF23" s="10">
+        <v>2843</v>
+      </c>
+      <c r="ABG23" s="10">
+        <v>1798</v>
+      </c>
+      <c r="ABH23" s="10">
+        <v>1301</v>
+      </c>
+      <c r="ABI23" s="10">
+        <v>117762</v>
+      </c>
+      <c r="ABJ23" s="10">
+        <v>120825</v>
+      </c>
+      <c r="ABK23" s="10">
+        <v>120826</v>
+      </c>
+      <c r="ABL23" s="10">
+        <v>121041</v>
+      </c>
+      <c r="ABM23" s="10">
+        <v>118684</v>
+      </c>
+      <c r="ABN23" s="10">
+        <v>115197</v>
+      </c>
+      <c r="ABO23" s="10">
+        <v>106231</v>
+      </c>
+      <c r="ABP23" s="10">
+        <v>96069</v>
+      </c>
+      <c r="ABQ23" s="10">
+        <v>83575</v>
+      </c>
+      <c r="ABR23" s="10">
+        <v>78185</v>
+      </c>
+      <c r="ABS23" s="10">
+        <v>76680</v>
+      </c>
+      <c r="ABT23" s="10">
+        <v>71869</v>
+      </c>
+      <c r="ABU23" s="10">
+        <v>66386</v>
+      </c>
+      <c r="ABV23" s="10">
+        <v>62541</v>
+      </c>
+      <c r="ABW23" s="10">
+        <v>57605</v>
+      </c>
+      <c r="ABX23" s="10">
+        <v>53606</v>
+      </c>
+      <c r="ABY23" s="10">
+        <v>50319</v>
+      </c>
+      <c r="ABZ23" s="10">
+        <v>49195</v>
+      </c>
+      <c r="ACA23" s="10">
+        <v>46047</v>
+      </c>
+      <c r="ACB23" s="10">
+        <v>43757</v>
+      </c>
+      <c r="ACC23" s="10">
+        <v>38810</v>
+      </c>
+      <c r="ACD23" s="10">
+        <v>36558</v>
+      </c>
+      <c r="ACE23" s="10">
+        <v>31865</v>
+      </c>
+      <c r="ACF23" s="10">
+        <v>28761</v>
+      </c>
+      <c r="ACG23" s="10">
+        <v>25494</v>
+      </c>
+      <c r="ACH23" s="10">
+        <v>21568</v>
+      </c>
+      <c r="ACI23" s="10">
+        <v>18171</v>
+      </c>
+      <c r="ACJ23" s="10">
+        <v>14493</v>
+      </c>
+      <c r="ACK23" s="10">
+        <v>12322</v>
+      </c>
+      <c r="ACL23" s="10">
+        <v>9963</v>
+      </c>
+      <c r="ACM23" s="10">
+        <v>6108</v>
+      </c>
+      <c r="ACN23" s="10">
+        <v>4238</v>
+      </c>
+      <c r="ACO23" s="10">
+        <v>3027</v>
+      </c>
+      <c r="ACP23" s="10">
+        <v>1965</v>
+      </c>
+      <c r="ACQ23" s="10">
+        <v>1188</v>
+      </c>
+      <c r="ACR23" s="10">
+        <v>113621</v>
+      </c>
+      <c r="ACS23" s="10">
+        <v>116632</v>
+      </c>
+      <c r="ACT23" s="10">
+        <v>119621</v>
+      </c>
+      <c r="ACU23" s="10">
+        <v>119458</v>
+      </c>
+      <c r="ACV23" s="10">
+        <v>119599</v>
+      </c>
+      <c r="ACW23" s="10">
+        <v>117113</v>
+      </c>
+      <c r="ACX23" s="10">
+        <v>113419</v>
+      </c>
+      <c r="ACY23" s="10">
+        <v>104443</v>
+      </c>
+      <c r="ACZ23" s="10">
+        <v>94357</v>
+      </c>
+      <c r="ADA23" s="10">
+        <v>81837</v>
+      </c>
+      <c r="ADB23" s="10">
+        <v>76379</v>
+      </c>
+      <c r="ADC23" s="10">
+        <v>74708</v>
+      </c>
+      <c r="ADD23" s="10">
+        <v>69855</v>
+      </c>
+      <c r="ADE23" s="10">
+        <v>64245</v>
+      </c>
+      <c r="ADF23" s="10">
+        <v>60290</v>
+      </c>
+      <c r="ADG23" s="10">
+        <v>55244</v>
+      </c>
+      <c r="ADH23" s="10">
+        <v>51049</v>
+      </c>
+      <c r="ADI23" s="10">
+        <v>47728</v>
+      </c>
+      <c r="ADJ23" s="10">
+        <v>46168</v>
+      </c>
+      <c r="ADK23" s="10">
+        <v>42990</v>
+      </c>
+      <c r="ADL23" s="10">
+        <v>40316</v>
+      </c>
+      <c r="ADM23" s="10">
+        <v>35432</v>
+      </c>
+      <c r="ADN23" s="10">
+        <v>32881</v>
+      </c>
+      <c r="ADO23" s="10">
+        <v>28370</v>
+      </c>
+      <c r="ADP23" s="10">
+        <v>25109</v>
+      </c>
+      <c r="ADQ23" s="10">
+        <v>21851</v>
+      </c>
+      <c r="ADR23" s="10">
+        <v>18170</v>
+      </c>
+      <c r="ADS23" s="10">
+        <v>14806</v>
+      </c>
+      <c r="ADT23" s="10">
+        <v>11550</v>
+      </c>
+      <c r="ADU23" s="10">
+        <v>9636</v>
+      </c>
+      <c r="ADV23" s="10">
+        <v>7567</v>
+      </c>
+      <c r="ADW23" s="10">
+        <v>4485</v>
+      </c>
+      <c r="ADX23" s="10">
+        <v>3016</v>
+      </c>
+      <c r="ADY23" s="10">
+        <v>2070</v>
+      </c>
+      <c r="ADZ23" s="10">
+        <v>1316</v>
+      </c>
+      <c r="AEA23" s="10">
+        <v>108662</v>
+      </c>
+      <c r="AEB23" s="10">
+        <v>112625</v>
+      </c>
+      <c r="AEC23" s="10">
+        <v>115530</v>
+      </c>
+      <c r="AED23" s="10">
+        <v>118331</v>
+      </c>
+      <c r="AEE23" s="10">
+        <v>118118</v>
+      </c>
+      <c r="AEF23" s="10">
+        <v>117978</v>
+      </c>
+      <c r="AEG23" s="10">
+        <v>115476</v>
+      </c>
+      <c r="AEH23" s="10">
+        <v>111472</v>
+      </c>
+      <c r="AEI23" s="10">
+        <v>102537</v>
+      </c>
+      <c r="AEJ23" s="10">
+        <v>92448</v>
+      </c>
+      <c r="AEK23" s="10">
+        <v>80107</v>
+      </c>
+      <c r="AEL23" s="10">
+        <v>74485</v>
+      </c>
+      <c r="AEM23" s="10">
+        <v>72620</v>
+      </c>
+      <c r="AEN23" s="10">
+        <v>67674</v>
+      </c>
+      <c r="AEO23" s="10">
+        <v>61900</v>
+      </c>
+      <c r="AEP23" s="10">
+        <v>57868</v>
+      </c>
+      <c r="AEQ23" s="10">
+        <v>52646</v>
+      </c>
+      <c r="AER23" s="10">
+        <v>48461</v>
+      </c>
+      <c r="AES23" s="10">
+        <v>44952</v>
+      </c>
+      <c r="AET23" s="10">
+        <v>43103</v>
+      </c>
+      <c r="AEU23" s="10">
+        <v>39712</v>
+      </c>
+      <c r="AEV23" s="10">
+        <v>36789</v>
+      </c>
+      <c r="AEW23" s="10">
+        <v>31966</v>
+      </c>
+      <c r="AEX23" s="10">
+        <v>29224</v>
+      </c>
+      <c r="AEY23" s="10">
+        <v>25054</v>
+      </c>
+      <c r="AEZ23" s="10">
+        <v>21492</v>
+      </c>
+      <c r="AFA23" s="10">
+        <v>18259</v>
+      </c>
+      <c r="AFB23" s="10">
+        <v>14989</v>
+      </c>
+      <c r="AFC23" s="10">
+        <v>11864</v>
+      </c>
+      <c r="AFD23" s="10">
+        <v>8960</v>
+      </c>
+      <c r="AFE23" s="10">
+        <v>7369</v>
+      </c>
+      <c r="AFF23" s="10">
+        <v>5544</v>
+      </c>
+      <c r="AFG23" s="10">
+        <v>3170</v>
+      </c>
+      <c r="AFH23" s="10">
+        <v>2065</v>
+      </c>
+      <c r="AFI23" s="10">
+        <v>1426</v>
+      </c>
+      <c r="AFJ23" s="10">
+        <v>109841</v>
+      </c>
+      <c r="AFK23" s="10">
+        <v>107721</v>
+      </c>
+      <c r="AFL23" s="10">
+        <v>111517</v>
+      </c>
+      <c r="AFM23" s="10">
+        <v>114318</v>
+      </c>
+      <c r="AFN23" s="10">
+        <v>116995</v>
+      </c>
+      <c r="AFO23" s="10">
+        <v>116520</v>
+      </c>
+      <c r="AFP23" s="10">
+        <v>116256</v>
+      </c>
+      <c r="AFQ23" s="10">
+        <v>113660</v>
+      </c>
+      <c r="AFR23" s="10">
+        <v>109518</v>
+      </c>
+      <c r="AFS23" s="10">
+        <v>100530</v>
+      </c>
+      <c r="AFT23" s="10">
+        <v>90457</v>
+      </c>
+      <c r="AFU23" s="10">
+        <v>78171</v>
+      </c>
+      <c r="AFV23" s="10">
+        <v>72401</v>
+      </c>
+      <c r="AFW23" s="10">
+        <v>70284</v>
+      </c>
+      <c r="AFX23" s="10">
+        <v>65287</v>
+      </c>
+      <c r="AFY23" s="10">
+        <v>59491</v>
+      </c>
+      <c r="AFZ23" s="10">
+        <v>55248</v>
+      </c>
+      <c r="AGA23" s="10">
+        <v>49960</v>
+      </c>
+      <c r="AGB23" s="10">
+        <v>45542</v>
+      </c>
+      <c r="AGC23" s="10">
+        <v>41880</v>
+      </c>
+      <c r="AGD23" s="10">
+        <v>39850</v>
+      </c>
+      <c r="AGE23" s="10">
+        <v>36338</v>
+      </c>
+      <c r="AGF23" s="10">
+        <v>33148</v>
+      </c>
+      <c r="AGG23" s="10">
+        <v>28337</v>
+      </c>
+      <c r="AGH23" s="10">
+        <v>25492</v>
+      </c>
+      <c r="AGI23" s="10">
+        <v>21393</v>
+      </c>
+      <c r="AGJ23" s="10">
+        <v>18054</v>
+      </c>
+      <c r="AGK23" s="10">
+        <v>15005</v>
+      </c>
+      <c r="AGL23" s="10">
+        <v>12021</v>
+      </c>
+      <c r="AGM23" s="10">
+        <v>9247</v>
+      </c>
+      <c r="AGN23" s="10">
+        <v>6749</v>
+      </c>
+      <c r="AGO23" s="10">
+        <v>5400</v>
+      </c>
+      <c r="AGP23" s="10">
+        <v>3968</v>
+      </c>
+      <c r="AGQ23" s="10">
+        <v>2132</v>
+      </c>
+      <c r="AGR23" s="10">
+        <v>1331</v>
+      </c>
+      <c r="AGS23" s="10">
+        <v>110550</v>
+      </c>
+      <c r="AGT23" s="10">
+        <v>108902</v>
+      </c>
+      <c r="AGU23" s="10">
+        <v>106604</v>
+      </c>
+      <c r="AGV23" s="10">
+        <v>110308</v>
+      </c>
+      <c r="AGW23" s="10">
+        <v>112947</v>
+      </c>
+      <c r="AGX23" s="10">
+        <v>115428</v>
+      </c>
+      <c r="AGY23" s="10">
+        <v>114877</v>
+      </c>
+      <c r="AGZ23" s="10">
+        <v>114340</v>
+      </c>
+      <c r="AHA23" s="10">
+        <v>111644</v>
+      </c>
+      <c r="AHB23" s="10">
+        <v>107359</v>
+      </c>
+      <c r="AHC23" s="10">
+        <v>98295</v>
+      </c>
+      <c r="AHD23" s="10">
+        <v>88283</v>
+      </c>
+      <c r="AHE23" s="10">
+        <v>76006</v>
+      </c>
+      <c r="AHF23" s="10">
+        <v>70129</v>
+      </c>
+      <c r="AHG23" s="10">
+        <v>67906</v>
+      </c>
+      <c r="AHH23" s="10">
+        <v>62709</v>
+      </c>
+      <c r="AHI23" s="10">
+        <v>56824</v>
+      </c>
+      <c r="AHJ23" s="10">
+        <v>52406</v>
+      </c>
+      <c r="AHK23" s="10">
+        <v>47049</v>
+      </c>
+      <c r="AHL23" s="10">
+        <v>42539</v>
+      </c>
+      <c r="AHM23" s="10">
+        <v>38765</v>
+      </c>
+      <c r="AHN23" s="10">
+        <v>36446</v>
+      </c>
+      <c r="AHO23" s="10">
+        <v>32839</v>
+      </c>
+      <c r="AHP23" s="10">
+        <v>29472</v>
+      </c>
+      <c r="AHQ23" s="10">
+        <v>24781</v>
+      </c>
+      <c r="AHR23" s="10">
+        <v>21788</v>
+      </c>
+      <c r="AHS23" s="10">
+        <v>18013</v>
+      </c>
+      <c r="AHT23" s="10">
+        <v>14932</v>
+      </c>
+      <c r="AHU23" s="10">
+        <v>12034</v>
+      </c>
+      <c r="AHV23" s="10">
+        <v>9480</v>
+      </c>
+      <c r="AHW23" s="10">
+        <v>7006</v>
+      </c>
+      <c r="AHX23" s="10">
+        <v>4983</v>
+      </c>
+      <c r="AHY23" s="10">
+        <v>3873</v>
+      </c>
+      <c r="AHZ23" s="10">
+        <v>2724</v>
+      </c>
+      <c r="AIA23" s="10">
+        <v>1403</v>
+      </c>
+      <c r="AIB23" s="10">
+        <v>108095</v>
+      </c>
+      <c r="AIC23" s="10">
+        <v>109510</v>
+      </c>
+      <c r="AID23" s="10">
+        <v>107927</v>
+      </c>
+      <c r="AIE23" s="10">
+        <v>105509</v>
+      </c>
+      <c r="AIF23" s="10">
+        <v>109007</v>
+      </c>
+      <c r="AIG23" s="10">
+        <v>111522</v>
+      </c>
+      <c r="AIH23" s="10">
+        <v>113904</v>
+      </c>
+      <c r="AII23" s="10">
+        <v>113141</v>
+      </c>
+      <c r="AIJ23" s="10">
+        <v>112310</v>
+      </c>
+      <c r="AIK23" s="10">
+        <v>109538</v>
+      </c>
+      <c r="AIL23" s="10">
+        <v>105077</v>
+      </c>
+      <c r="AIM23" s="10">
+        <v>95932</v>
+      </c>
+      <c r="AIN23" s="10">
+        <v>85993</v>
+      </c>
+      <c r="AIO23" s="10">
+        <v>73767</v>
+      </c>
+      <c r="AIP23" s="10">
+        <v>67829</v>
+      </c>
+      <c r="AIQ23" s="10">
+        <v>65302</v>
+      </c>
+      <c r="AIR23" s="10">
+        <v>60124</v>
+      </c>
+      <c r="AIS23" s="10">
+        <v>54029</v>
+      </c>
+      <c r="AIT23" s="10">
+        <v>49510</v>
+      </c>
+      <c r="AIU23" s="10">
+        <v>44085</v>
+      </c>
+      <c r="AIV23" s="10">
+        <v>39486</v>
+      </c>
+      <c r="AIW23" s="10">
+        <v>35646</v>
+      </c>
+      <c r="AIX23" s="10">
+        <v>33049</v>
+      </c>
+      <c r="AIY23" s="10">
+        <v>29430</v>
+      </c>
+      <c r="AIZ23" s="10">
+        <v>26018</v>
+      </c>
+      <c r="AJA23" s="10">
+        <v>21450</v>
+      </c>
+      <c r="AJB23" s="10">
+        <v>18531</v>
+      </c>
+      <c r="AJC23" s="10">
+        <v>15006</v>
+      </c>
+      <c r="AJD23" s="10">
+        <v>12119</v>
+      </c>
+      <c r="AJE23" s="10">
+        <v>9538</v>
+      </c>
+      <c r="AJF23" s="10">
+        <v>7317</v>
+      </c>
+      <c r="AJG23" s="10">
+        <v>5241</v>
+      </c>
+      <c r="AJH23" s="10">
+        <v>3655</v>
+      </c>
+      <c r="AJI23" s="10">
+        <v>2709</v>
+      </c>
+      <c r="AJJ23" s="10">
+        <v>1854</v>
+      </c>
+      <c r="AJK23" s="10">
+        <v>110223</v>
+      </c>
+      <c r="AJL23" s="10">
+        <v>107098</v>
+      </c>
+      <c r="AJM23" s="10">
+        <v>108404</v>
+      </c>
+      <c r="AJN23" s="10">
+        <v>106751</v>
+      </c>
+      <c r="AJO23" s="10">
+        <v>104258</v>
+      </c>
+      <c r="AJP23" s="10">
+        <v>107566</v>
+      </c>
+      <c r="AJQ23" s="10">
+        <v>109846</v>
+      </c>
+      <c r="AJR23" s="10">
+        <v>112058</v>
+      </c>
+      <c r="AJS23" s="10">
+        <v>111095</v>
+      </c>
+      <c r="AJT23" s="10">
+        <v>110052</v>
+      </c>
+      <c r="AJU23" s="10">
+        <v>107099</v>
+      </c>
+      <c r="AJV23" s="10">
+        <v>102442</v>
+      </c>
+      <c r="AJW23" s="10">
+        <v>93151</v>
+      </c>
+      <c r="AJX23" s="10">
+        <v>83344</v>
+      </c>
+      <c r="AJY23" s="10">
+        <v>70979</v>
+      </c>
+      <c r="AJZ23" s="10">
+        <v>65042</v>
+      </c>
+      <c r="AKA23" s="10">
+        <v>62228</v>
+      </c>
+      <c r="AKB23" s="10">
+        <v>56875</v>
+      </c>
+      <c r="AKC23" s="10">
+        <v>50651</v>
+      </c>
+      <c r="AKD23" s="10">
+        <v>46234</v>
+      </c>
+      <c r="AKE23" s="10">
+        <v>40534</v>
+      </c>
+      <c r="AKF23" s="10">
+        <v>35935</v>
+      </c>
+      <c r="AKG23" s="10">
+        <v>32151</v>
+      </c>
+      <c r="AKH23" s="10">
+        <v>29194</v>
+      </c>
+      <c r="AKI23" s="10">
+        <v>25560</v>
+      </c>
+      <c r="AKJ23" s="10">
+        <v>22125</v>
+      </c>
+      <c r="AKK23" s="10">
+        <v>17922</v>
+      </c>
+      <c r="AKL23" s="10">
+        <v>15086</v>
+      </c>
+      <c r="AKM23" s="10">
+        <v>11928</v>
+      </c>
+      <c r="AKN23" s="10">
+        <v>9315</v>
+      </c>
+      <c r="AKO23" s="10">
+        <v>7135</v>
+      </c>
+      <c r="AKP23" s="10">
+        <v>5361</v>
+      </c>
+      <c r="AKQ23" s="10">
+        <v>3710</v>
+      </c>
+      <c r="AKR23" s="10">
+        <v>2515</v>
+      </c>
+      <c r="AKS23" s="10">
+        <v>1770</v>
+      </c>
+      <c r="AKT23" s="10">
+        <v>112116</v>
+      </c>
+      <c r="AKU23" s="10">
+        <v>109244</v>
+      </c>
+      <c r="AKV23" s="10">
+        <v>106045</v>
+      </c>
+      <c r="AKW23" s="10">
+        <v>107279</v>
+      </c>
+      <c r="AKX23" s="10">
+        <v>105536</v>
+      </c>
+      <c r="AKY23" s="10">
+        <v>102886</v>
+      </c>
+      <c r="AKZ23" s="10">
+        <v>105990</v>
+      </c>
+      <c r="ALA23" s="10">
+        <v>108111</v>
+      </c>
+      <c r="ALB23" s="10">
+        <v>110180</v>
+      </c>
+      <c r="ALC23" s="10">
+        <v>108949</v>
+      </c>
+      <c r="ALD23" s="10">
+        <v>107685</v>
+      </c>
+      <c r="ALE23" s="10">
+        <v>104546</v>
+      </c>
+      <c r="ALF23" s="10">
+        <v>99697</v>
+      </c>
+      <c r="ALG23" s="10">
+        <v>90315</v>
+      </c>
+      <c r="ALH23" s="10">
+        <v>80553</v>
+      </c>
+      <c r="ALI23" s="10">
+        <v>68279</v>
+      </c>
+      <c r="ALJ23" s="10">
+        <v>62285</v>
+      </c>
+      <c r="ALK23" s="10">
+        <v>59265</v>
+      </c>
+      <c r="ALL23" s="10">
+        <v>53748</v>
+      </c>
+      <c r="ALM23" s="10">
+        <v>47434</v>
+      </c>
+      <c r="ALN23" s="10">
+        <v>42966</v>
+      </c>
+      <c r="ALO23" s="10">
+        <v>37186</v>
+      </c>
+      <c r="ALP23" s="10">
+        <v>32671</v>
+      </c>
+      <c r="ALQ23" s="10">
+        <v>28783</v>
+      </c>
+      <c r="ALR23" s="10">
+        <v>25715</v>
+      </c>
+      <c r="ALS23" s="10">
+        <v>22208</v>
+      </c>
+      <c r="ALT23" s="10">
+        <v>18804</v>
+      </c>
+      <c r="ALU23" s="10">
+        <v>14969</v>
+      </c>
+      <c r="ALV23" s="10">
+        <v>12268</v>
+      </c>
+      <c r="ALW23" s="10">
+        <v>9499</v>
+      </c>
+      <c r="ALX23" s="10">
+        <v>7236</v>
+      </c>
+      <c r="ALY23" s="10">
+        <v>5344</v>
+      </c>
+      <c r="ALZ23" s="10">
+        <v>3944</v>
+      </c>
+      <c r="AMA23" s="10">
+        <v>2639</v>
+      </c>
+      <c r="AMB23" s="10">
+        <v>1729</v>
+      </c>
+      <c r="AMC23" s="10">
+        <v>112055</v>
+      </c>
+      <c r="AMD23" s="10">
+        <v>111275</v>
+      </c>
+      <c r="AME23" s="10">
+        <v>108290</v>
+      </c>
+      <c r="AMF23" s="10">
+        <v>104990</v>
+      </c>
+      <c r="AMG23" s="10">
+        <v>106130</v>
+      </c>
+      <c r="AMH23" s="10">
+        <v>104165</v>
+      </c>
+      <c r="AMI23" s="10">
+        <v>101489</v>
+      </c>
+      <c r="AMJ23" s="10">
+        <v>104335</v>
+      </c>
+      <c r="AMK23" s="10">
+        <v>106311</v>
+      </c>
+      <c r="AML23" s="10">
+        <v>108083</v>
+      </c>
+      <c r="AMM23" s="10">
+        <v>106730</v>
+      </c>
+      <c r="AMN23" s="10">
+        <v>105197</v>
+      </c>
+      <c r="AMO23" s="10">
+        <v>101810</v>
+      </c>
+      <c r="AMP23" s="10">
+        <v>96645</v>
+      </c>
+      <c r="AMQ23" s="10">
+        <v>87285</v>
+      </c>
+      <c r="AMR23" s="10">
+        <v>77551</v>
+      </c>
+      <c r="AMS23" s="10">
+        <v>65310</v>
+      </c>
+      <c r="AMT23" s="10">
+        <v>59186</v>
+      </c>
+      <c r="AMU23" s="10">
+        <v>55885</v>
+      </c>
+      <c r="AMV23" s="10">
+        <v>50399</v>
+      </c>
+      <c r="AMW23" s="10">
+        <v>44024</v>
+      </c>
+      <c r="AMX23" s="10">
+        <v>39516</v>
+      </c>
+      <c r="AMY23" s="10">
+        <v>33810</v>
+      </c>
+      <c r="AMZ23" s="10">
+        <v>29260</v>
+      </c>
+      <c r="ANA23" s="10">
+        <v>25343</v>
+      </c>
+      <c r="ANB23" s="10">
+        <v>22313</v>
+      </c>
+      <c r="ANC23" s="10">
+        <v>18751</v>
+      </c>
+      <c r="AND23" s="10">
+        <v>15599</v>
+      </c>
+      <c r="ANE23" s="10">
+        <v>12078</v>
+      </c>
+      <c r="ANF23" s="10">
+        <v>9646</v>
+      </c>
+      <c r="ANG23" s="10">
+        <v>7263</v>
+      </c>
+      <c r="ANH23" s="10">
+        <v>5413</v>
+      </c>
+      <c r="ANI23" s="10">
+        <v>3811</v>
+      </c>
+      <c r="ANJ23" s="10">
+        <v>2733</v>
+      </c>
+      <c r="ANK23" s="10">
+        <v>1769</v>
+      </c>
+      <c r="ANL23" s="10">
+        <v>111147</v>
+      </c>
+      <c r="ANM23" s="10">
+        <v>111138</v>
+      </c>
+      <c r="ANN23" s="10">
+        <v>110302</v>
+      </c>
+      <c r="ANO23" s="10">
+        <v>107262</v>
+      </c>
+      <c r="ANP23" s="10">
+        <v>103870</v>
+      </c>
+      <c r="ANQ23" s="10">
+        <v>104851</v>
+      </c>
+      <c r="ANR23" s="10">
+        <v>102805</v>
+      </c>
+      <c r="ANS23" s="10">
+        <v>99923</v>
+      </c>
+      <c r="ANT23" s="10">
+        <v>102660</v>
+      </c>
+      <c r="ANU23" s="10">
+        <v>104398</v>
+      </c>
+      <c r="ANV23" s="10">
+        <v>105825</v>
+      </c>
+      <c r="ANW23" s="10">
+        <v>104266</v>
+      </c>
+      <c r="ANX23" s="10">
+        <v>102537</v>
+      </c>
+      <c r="ANY23" s="10">
+        <v>98769</v>
+      </c>
+      <c r="ANZ23" s="10">
+        <v>93443</v>
+      </c>
+      <c r="AOA23" s="10">
+        <v>84121</v>
+      </c>
+      <c r="AOB23" s="10">
+        <v>74402</v>
+      </c>
+      <c r="AOC23" s="10">
+        <v>62214</v>
+      </c>
+      <c r="AOD23" s="10">
+        <v>56046</v>
+      </c>
+      <c r="AOE23" s="10">
+        <v>52464</v>
+      </c>
+      <c r="AOF23" s="10">
+        <v>46932</v>
+      </c>
+      <c r="AOG23" s="10">
+        <v>40534</v>
+      </c>
+      <c r="AOH23" s="10">
+        <v>35960</v>
+      </c>
+      <c r="AOI23" s="10">
+        <v>30336</v>
+      </c>
+      <c r="AOJ23" s="10">
+        <v>25863</v>
+      </c>
+      <c r="AOK23" s="10">
+        <v>22020</v>
+      </c>
+      <c r="AOL23" s="10">
+        <v>19021</v>
+      </c>
+      <c r="AOM23" s="10">
+        <v>15606</v>
+      </c>
+      <c r="AON23" s="10">
+        <v>12604</v>
+      </c>
+      <c r="AOO23" s="10">
+        <v>9570</v>
+      </c>
+      <c r="AOP23" s="10">
+        <v>7339</v>
+      </c>
+      <c r="AOQ23" s="10">
+        <v>5382</v>
+      </c>
+      <c r="AOR23" s="10">
+        <v>3855</v>
+      </c>
+      <c r="AOS23" s="10">
+        <v>2674</v>
+      </c>
+      <c r="AOT23" s="10">
+        <v>1863</v>
       </c>
     </row>
-    <row r="24" spans="1:1086" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="MN24" s="9">
-        <v>86863</v>
-      </c>
-      <c r="MO24" s="9">
-        <v>82140</v>
-      </c>
-      <c r="MP24" s="9">
-        <v>79198</v>
-      </c>
-      <c r="MQ24" s="9">
-        <v>75074</v>
-      </c>
-      <c r="MR24" s="9">
-        <v>72402</v>
-      </c>
-      <c r="MS24" s="9">
-        <v>70149</v>
-      </c>
-      <c r="MT24" s="9">
-        <v>71881</v>
-      </c>
-      <c r="MU24" s="9">
-        <v>70591</v>
-      </c>
-      <c r="MV24" s="9">
-        <v>70644</v>
-      </c>
-      <c r="MW24" s="9">
-        <v>67132</v>
-      </c>
-      <c r="MX24" s="9">
-        <v>67807</v>
-      </c>
-      <c r="MY24" s="9">
-        <v>64345</v>
-      </c>
-      <c r="MZ24" s="9">
-        <v>63666</v>
-      </c>
-      <c r="NA24" s="9">
-        <v>62912</v>
-      </c>
-      <c r="NB24" s="9">
-        <v>60512</v>
-      </c>
-      <c r="NC24" s="9">
-        <v>58581</v>
-      </c>
-      <c r="ND24" s="9">
-        <v>55117</v>
-      </c>
-      <c r="NE24" s="9">
-        <v>55363</v>
-      </c>
-      <c r="NF24" s="9">
-        <v>53694</v>
-      </c>
-      <c r="NG24" s="9">
-        <v>40438</v>
-      </c>
-      <c r="NH24" s="9">
-        <v>36271</v>
-      </c>
-      <c r="NI24" s="9">
-        <v>32715</v>
-      </c>
-      <c r="NJ24" s="9">
-        <v>28297</v>
-      </c>
-      <c r="NK24" s="9">
-        <v>23947</v>
-      </c>
-      <c r="NL24" s="9">
-        <v>21001</v>
-      </c>
-      <c r="NM24" s="9">
-        <v>17438</v>
-      </c>
-      <c r="NN24" s="9">
-        <v>14244</v>
-      </c>
-      <c r="NO24" s="9">
-        <v>10961</v>
-      </c>
-      <c r="NP24" s="9">
-        <v>8379</v>
-      </c>
-      <c r="NQ24" s="9">
-        <v>6400</v>
-      </c>
-      <c r="NR24" s="9">
-        <v>4482</v>
-      </c>
-      <c r="NS24" s="9">
-        <v>3144</v>
-      </c>
-      <c r="NT24" s="9">
-        <v>2108</v>
-      </c>
-      <c r="NU24" s="9">
-        <v>1319</v>
-      </c>
-      <c r="NV24" s="9">
-        <v>839</v>
-      </c>
-      <c r="NW24" s="9">
-        <v>90241</v>
-      </c>
-      <c r="NX24" s="9">
-        <v>85877</v>
-      </c>
-      <c r="NY24" s="9">
-        <v>81117</v>
-      </c>
-      <c r="NZ24" s="9">
-        <v>78125</v>
-      </c>
-      <c r="OA24" s="9">
-        <v>73888</v>
-      </c>
-      <c r="OB24" s="9">
-        <v>71193</v>
-      </c>
-      <c r="OC24" s="9">
-        <v>68795</v>
-      </c>
-      <c r="OD24" s="9">
-        <v>70363</v>
-      </c>
-      <c r="OE24" s="9">
-        <v>69016</v>
-      </c>
-      <c r="OF24" s="9">
-        <v>68826</v>
-      </c>
-      <c r="OG24" s="9">
-        <v>65259</v>
-      </c>
-      <c r="OH24" s="9">
-        <v>65780</v>
-      </c>
-      <c r="OI24" s="9">
-        <v>62086</v>
-      </c>
-      <c r="OJ24" s="9">
-        <v>61236</v>
-      </c>
-      <c r="OK24" s="9">
-        <v>60196</v>
-      </c>
-      <c r="OL24" s="9">
-        <v>57632</v>
-      </c>
-      <c r="OM24" s="9">
-        <v>55350</v>
-      </c>
-      <c r="ON24" s="9">
-        <v>51691</v>
-      </c>
-      <c r="OO24" s="9">
-        <v>51546</v>
-      </c>
-      <c r="OP24" s="9">
-        <v>49463</v>
-      </c>
-      <c r="OQ24" s="9">
-        <v>36903</v>
-      </c>
-      <c r="OR24" s="9">
-        <v>32560</v>
-      </c>
-      <c r="OS24" s="9">
-        <v>29075</v>
-      </c>
-      <c r="OT24" s="9">
-        <v>24722</v>
-      </c>
-      <c r="OU24" s="9">
-        <v>20553</v>
-      </c>
-      <c r="OV24" s="9">
-        <v>17712</v>
-      </c>
-      <c r="OW24" s="9">
-        <v>14459</v>
-      </c>
-      <c r="OX24" s="9">
-        <v>11588</v>
-      </c>
-      <c r="OY24" s="9">
-        <v>8705</v>
-      </c>
-      <c r="OZ24" s="9">
-        <v>6470</v>
-      </c>
-      <c r="PA24" s="9">
-        <v>4794</v>
-      </c>
-      <c r="PB24" s="9">
-        <v>3278</v>
-      </c>
-      <c r="PC24" s="9">
-        <v>2227</v>
-      </c>
-      <c r="PD24" s="9">
-        <v>1456</v>
-      </c>
-      <c r="PE24" s="9">
-        <v>875</v>
-      </c>
-      <c r="PF24" s="9">
-        <v>89319</v>
-      </c>
-      <c r="PG24" s="9">
-        <v>89192</v>
-      </c>
-      <c r="PH24" s="9">
-        <v>84742</v>
-      </c>
-      <c r="PI24" s="9">
-        <v>80017</v>
-      </c>
-      <c r="PJ24" s="9">
-        <v>76991</v>
-      </c>
-      <c r="PK24" s="9">
-        <v>72627</v>
-      </c>
-      <c r="PL24" s="9">
-        <v>69903</v>
-      </c>
-      <c r="PM24" s="9">
-        <v>67452</v>
-      </c>
-      <c r="PN24" s="9">
-        <v>68803</v>
-      </c>
-      <c r="PO24" s="9">
-        <v>67230</v>
-      </c>
-      <c r="PP24" s="9">
-        <v>66855</v>
-      </c>
-      <c r="PQ24" s="9">
-        <v>63338</v>
-      </c>
-      <c r="PR24" s="9">
-        <v>63480</v>
-      </c>
-      <c r="PS24" s="9">
-        <v>59721</v>
-      </c>
-      <c r="PT24" s="9">
-        <v>58544</v>
-      </c>
-      <c r="PU24" s="9">
-        <v>57215</v>
-      </c>
-      <c r="PV24" s="9">
-        <v>54454</v>
-      </c>
-      <c r="PW24" s="9">
-        <v>51994</v>
-      </c>
-      <c r="PX24" s="9">
-        <v>47964</v>
-      </c>
-      <c r="PY24" s="9">
-        <v>47594</v>
-      </c>
-      <c r="PZ24" s="9">
-        <v>45059</v>
-      </c>
-      <c r="QA24" s="9">
-        <v>33284</v>
-      </c>
-      <c r="QB24" s="9">
-        <v>28865</v>
-      </c>
-      <c r="QC24" s="9">
-        <v>25400</v>
-      </c>
-      <c r="QD24" s="9">
-        <v>21268</v>
-      </c>
-      <c r="QE24" s="9">
-        <v>17327</v>
-      </c>
-      <c r="QF24" s="9">
-        <v>14680</v>
-      </c>
-      <c r="QG24" s="9">
-        <v>11718</v>
-      </c>
-      <c r="QH24" s="9">
-        <v>9098</v>
-      </c>
-      <c r="QI24" s="9">
-        <v>6689</v>
-      </c>
-      <c r="QJ24" s="9">
-        <v>4861</v>
-      </c>
-      <c r="QK24" s="9">
-        <v>3521</v>
-      </c>
-      <c r="QL24" s="9">
-        <v>2345</v>
-      </c>
-      <c r="QM24" s="9">
-        <v>1519</v>
-      </c>
-      <c r="QN24" s="9">
-        <v>966</v>
-      </c>
-      <c r="QO24" s="9">
-        <v>93339</v>
-      </c>
-      <c r="QP24" s="9">
-        <v>88347</v>
-      </c>
-      <c r="QQ24" s="9">
-        <v>88224</v>
-      </c>
-      <c r="QR24" s="9">
-        <v>83695</v>
-      </c>
-      <c r="QS24" s="9">
-        <v>78949</v>
-      </c>
-      <c r="QT24" s="9">
-        <v>75771</v>
-      </c>
-      <c r="QU24" s="9">
-        <v>71364</v>
-      </c>
-      <c r="QV24" s="9">
-        <v>68460</v>
-      </c>
-      <c r="QW24" s="9">
-        <v>66032</v>
-      </c>
-      <c r="QX24" s="9">
-        <v>67167</v>
-      </c>
-      <c r="QY24" s="9">
-        <v>65421</v>
-      </c>
-      <c r="QZ24" s="9">
-        <v>64921</v>
-      </c>
-      <c r="RA24" s="9">
-        <v>61210</v>
-      </c>
-      <c r="RB24" s="9">
-        <v>61093</v>
-      </c>
-      <c r="RC24" s="9">
-        <v>57190</v>
-      </c>
-      <c r="RD24" s="9">
-        <v>55811</v>
-      </c>
-      <c r="RE24" s="9">
-        <v>54132</v>
-      </c>
-      <c r="RF24" s="9">
-        <v>51161</v>
-      </c>
-      <c r="RG24" s="9">
-        <v>48517</v>
-      </c>
-      <c r="RH24" s="9">
-        <v>44190</v>
-      </c>
-      <c r="RI24" s="9">
-        <v>43398</v>
-      </c>
-      <c r="RJ24" s="9">
-        <v>40609</v>
-      </c>
-      <c r="RK24" s="9">
-        <v>29729</v>
-      </c>
-      <c r="RL24" s="9">
-        <v>25281</v>
-      </c>
-      <c r="RM24" s="9">
-        <v>21829</v>
-      </c>
-      <c r="RN24" s="9">
-        <v>17993</v>
-      </c>
-      <c r="RO24" s="9">
-        <v>14372</v>
-      </c>
-      <c r="RP24" s="9">
-        <v>11853</v>
-      </c>
-      <c r="RQ24" s="9">
-        <v>9273</v>
-      </c>
-      <c r="RR24" s="9">
-        <v>7098</v>
-      </c>
-      <c r="RS24" s="9">
-        <v>4985</v>
-      </c>
-      <c r="RT24" s="9">
-        <v>3524</v>
-      </c>
-      <c r="RU24" s="9">
-        <v>2475</v>
-      </c>
-      <c r="RV24" s="9">
-        <v>1634</v>
-      </c>
-      <c r="RW24" s="9">
-        <v>983</v>
-      </c>
-      <c r="RX24" s="9">
-        <v>105147</v>
-      </c>
-      <c r="RY24" s="9">
-        <v>92288</v>
-      </c>
-      <c r="RZ24" s="9">
-        <v>87351</v>
-      </c>
-      <c r="SA24" s="9">
-        <v>87089</v>
-      </c>
-      <c r="SB24" s="9">
-        <v>82611</v>
-      </c>
-      <c r="SC24" s="9">
-        <v>77707</v>
-      </c>
-      <c r="SD24" s="9">
-        <v>74553</v>
-      </c>
-      <c r="SE24" s="9">
-        <v>70042</v>
-      </c>
-      <c r="SF24" s="9">
-        <v>66978</v>
-      </c>
-      <c r="SG24" s="9">
-        <v>64554</v>
-      </c>
-      <c r="SH24" s="9">
-        <v>65438</v>
-      </c>
-      <c r="SI24" s="9">
-        <v>63453</v>
-      </c>
-      <c r="SJ24" s="9">
-        <v>62808</v>
-      </c>
-      <c r="SK24" s="9">
-        <v>58863</v>
-      </c>
-      <c r="SL24" s="9">
-        <v>58569</v>
-      </c>
-      <c r="SM24" s="9">
-        <v>54474</v>
-      </c>
-      <c r="SN24" s="9">
-        <v>52806</v>
-      </c>
-      <c r="SO24" s="9">
-        <v>50845</v>
-      </c>
-      <c r="SP24" s="9">
-        <v>47641</v>
-      </c>
-      <c r="SQ24" s="9">
-        <v>44904</v>
-      </c>
-      <c r="SR24" s="9">
-        <v>40296</v>
-      </c>
-      <c r="SS24" s="9">
-        <v>39193</v>
-      </c>
-      <c r="ST24" s="9">
-        <v>36118</v>
-      </c>
-      <c r="SU24" s="9">
-        <v>26053</v>
-      </c>
-      <c r="SV24" s="9">
-        <v>21704</v>
-      </c>
-      <c r="SW24" s="9">
-        <v>18449</v>
-      </c>
-      <c r="SX24" s="9">
-        <v>14915</v>
-      </c>
-      <c r="SY24" s="9">
-        <v>11652</v>
-      </c>
-      <c r="SZ24" s="9">
-        <v>9289</v>
-      </c>
-      <c r="TA24" s="9">
-        <v>7061</v>
-      </c>
-      <c r="TB24" s="9">
-        <v>5306</v>
-      </c>
-      <c r="TC24" s="9">
-        <v>3564</v>
-      </c>
-      <c r="TD24" s="9">
-        <v>2489</v>
-      </c>
-      <c r="TE24" s="9">
-        <v>1655</v>
-      </c>
-      <c r="TF24" s="9">
-        <v>1090</v>
-      </c>
-      <c r="TG24" s="9">
-        <v>114389</v>
-      </c>
-      <c r="TH24" s="9">
-        <v>104072</v>
-      </c>
-      <c r="TI24" s="9">
-        <v>91217</v>
-      </c>
-      <c r="TJ24" s="9">
-        <v>86332</v>
-      </c>
-      <c r="TK24" s="9">
-        <v>85811</v>
-      </c>
-      <c r="TL24" s="9">
-        <v>81385</v>
-      </c>
-      <c r="TM24" s="9">
-        <v>76448</v>
-      </c>
-      <c r="TN24" s="9">
-        <v>73193</v>
-      </c>
-      <c r="TO24" s="9">
-        <v>68667</v>
-      </c>
-      <c r="TP24" s="9">
-        <v>65419</v>
-      </c>
-      <c r="TQ24" s="9">
-        <v>62888</v>
-      </c>
-      <c r="TR24" s="9">
-        <v>63609</v>
-      </c>
-      <c r="TS24" s="9">
-        <v>61451</v>
-      </c>
-      <c r="TT24" s="9">
-        <v>60538</v>
-      </c>
-      <c r="TU24" s="9">
-        <v>56549</v>
-      </c>
-      <c r="TV24" s="9">
-        <v>55907</v>
-      </c>
-      <c r="TW24" s="9">
-        <v>51528</v>
-      </c>
-      <c r="TX24" s="9">
-        <v>49729</v>
-      </c>
-      <c r="TY24" s="9">
-        <v>47387</v>
-      </c>
-      <c r="TZ24" s="9">
-        <v>44053</v>
-      </c>
-      <c r="UA24" s="9">
-        <v>41085</v>
-      </c>
-      <c r="UB24" s="9">
-        <v>36353</v>
-      </c>
-      <c r="UC24" s="9">
-        <v>34942</v>
-      </c>
-      <c r="UD24" s="9">
-        <v>31666</v>
-      </c>
-      <c r="UE24" s="9">
-        <v>22491</v>
-      </c>
-      <c r="UF24" s="9">
-        <v>18266</v>
-      </c>
-      <c r="UG24" s="9">
-        <v>15285</v>
-      </c>
-      <c r="UH24" s="9">
-        <v>12048</v>
-      </c>
-      <c r="UI24" s="9">
-        <v>9158</v>
-      </c>
-      <c r="UJ24" s="9">
-        <v>7185</v>
-      </c>
-      <c r="UK24" s="9">
-        <v>5350</v>
-      </c>
-      <c r="UL24" s="9">
-        <v>3816</v>
-      </c>
-      <c r="UM24" s="9">
-        <v>2535</v>
-      </c>
-      <c r="UN24" s="9">
-        <v>1692</v>
-      </c>
-      <c r="UO24" s="9">
-        <v>1092</v>
-      </c>
-      <c r="UP24" s="9">
-        <v>121996</v>
-      </c>
-      <c r="UQ24" s="9">
-        <v>113294</v>
-      </c>
-      <c r="UR24" s="9">
-        <v>103011</v>
-      </c>
-      <c r="US24" s="9">
-        <v>90193</v>
-      </c>
-      <c r="UT24" s="9">
-        <v>85263</v>
-      </c>
-      <c r="UU24" s="9">
-        <v>84557</v>
-      </c>
-      <c r="UV24" s="9">
-        <v>80133</v>
-      </c>
-      <c r="UW24" s="9">
-        <v>75096</v>
-      </c>
-      <c r="UX24" s="9">
-        <v>71680</v>
-      </c>
-      <c r="UY24" s="9">
-        <v>67108</v>
-      </c>
-      <c r="UZ24" s="9">
-        <v>63750</v>
-      </c>
-      <c r="VA24" s="9">
-        <v>61169</v>
-      </c>
-      <c r="VB24" s="9">
-        <v>61652</v>
-      </c>
-      <c r="VC24" s="9">
-        <v>59306</v>
-      </c>
-      <c r="VD24" s="9">
-        <v>58184</v>
-      </c>
-      <c r="VE24" s="9">
-        <v>53981</v>
-      </c>
-      <c r="VF24" s="9">
-        <v>53105</v>
-      </c>
-      <c r="VG24" s="9">
-        <v>48617</v>
-      </c>
-      <c r="VH24" s="9">
-        <v>46603</v>
-      </c>
-      <c r="VI24" s="9">
-        <v>43903</v>
-      </c>
-      <c r="VJ24" s="9">
-        <v>40365</v>
-      </c>
-      <c r="VK24" s="9">
-        <v>37203</v>
-      </c>
-      <c r="VL24" s="9">
-        <v>32502</v>
-      </c>
-      <c r="VM24" s="9">
-        <v>30753</v>
-      </c>
-      <c r="VN24" s="9">
-        <v>27372</v>
-      </c>
-      <c r="VO24" s="9">
-        <v>19120</v>
-      </c>
-      <c r="VP24" s="9">
-        <v>15292</v>
-      </c>
-      <c r="VQ24" s="9">
-        <v>12499</v>
-      </c>
-      <c r="VR24" s="9">
-        <v>9547</v>
-      </c>
-      <c r="VS24" s="9">
-        <v>6993</v>
-      </c>
-      <c r="VT24" s="9">
-        <v>5417</v>
-      </c>
-      <c r="VU24" s="9">
-        <v>3936</v>
-      </c>
-      <c r="VV24" s="9">
-        <v>2722</v>
-      </c>
-      <c r="VW24" s="9">
-        <v>1732</v>
-      </c>
-      <c r="VX24" s="9">
-        <v>1087</v>
-      </c>
-      <c r="VY24" s="9">
-        <v>123950</v>
-      </c>
-      <c r="VZ24" s="9">
-        <v>120794</v>
-      </c>
-      <c r="WA24" s="9">
-        <v>112085</v>
-      </c>
-      <c r="WB24" s="9">
-        <v>101818</v>
-      </c>
-      <c r="WC24" s="9">
-        <v>89038</v>
-      </c>
-      <c r="WD24" s="9">
-        <v>83971</v>
-      </c>
-      <c r="WE24" s="9">
-        <v>83221</v>
-      </c>
-      <c r="WF24" s="9">
-        <v>78742</v>
-      </c>
-      <c r="WG24" s="9">
-        <v>73610</v>
-      </c>
-      <c r="WH24" s="9">
-        <v>70071</v>
-      </c>
-      <c r="WI24" s="9">
-        <v>65447</v>
-      </c>
-      <c r="WJ24" s="9">
-        <v>61982</v>
-      </c>
-      <c r="WK24" s="9">
-        <v>59287</v>
-      </c>
-      <c r="WL24" s="9">
-        <v>59438</v>
-      </c>
-      <c r="WM24" s="9">
-        <v>56888</v>
-      </c>
-      <c r="WN24" s="9">
-        <v>55651</v>
-      </c>
-      <c r="WO24" s="9">
-        <v>51235</v>
-      </c>
-      <c r="WP24" s="9">
-        <v>50088</v>
-      </c>
-      <c r="WQ24" s="9">
-        <v>45476</v>
-      </c>
-      <c r="WR24" s="9">
-        <v>43237</v>
-      </c>
-      <c r="WS24" s="9">
-        <v>40351</v>
-      </c>
-      <c r="WT24" s="9">
-        <v>36588</v>
-      </c>
-      <c r="WU24" s="9">
-        <v>33288</v>
-      </c>
-      <c r="WV24" s="9">
-        <v>28598</v>
-      </c>
-      <c r="WW24" s="9">
-        <v>26649</v>
-      </c>
-      <c r="WX24" s="9">
-        <v>23310</v>
-      </c>
-      <c r="WY24" s="9">
-        <v>15848</v>
-      </c>
-      <c r="WZ24" s="9">
-        <v>12447</v>
-      </c>
-      <c r="XA24" s="9">
-        <v>9965</v>
-      </c>
-      <c r="XB24" s="9">
-        <v>7342</v>
-      </c>
-      <c r="XC24" s="9">
-        <v>5276</v>
-      </c>
-      <c r="XD24" s="9">
-        <v>4000</v>
-      </c>
-      <c r="XE24" s="9">
-        <v>2816</v>
-      </c>
-      <c r="XF24" s="9">
-        <v>1905</v>
-      </c>
-      <c r="XG24" s="9">
-        <v>1175</v>
-      </c>
-      <c r="XH24" s="9">
-        <v>124876</v>
-      </c>
-      <c r="XI24" s="9">
-        <v>122744</v>
-      </c>
-      <c r="XJ24" s="9">
-        <v>119515</v>
-      </c>
-      <c r="XK24" s="9">
-        <v>110835</v>
-      </c>
-      <c r="XL24" s="9">
-        <v>100493</v>
-      </c>
-      <c r="XM24" s="9">
-        <v>87771</v>
-      </c>
-      <c r="XN24" s="9">
-        <v>82656</v>
-      </c>
-      <c r="XO24" s="9">
-        <v>81757</v>
-      </c>
-      <c r="XP24" s="9">
-        <v>77224</v>
-      </c>
-      <c r="XQ24" s="9">
-        <v>72024</v>
-      </c>
-      <c r="XR24" s="9">
-        <v>68465</v>
-      </c>
-      <c r="XS24" s="9">
-        <v>63635</v>
-      </c>
-      <c r="XT24" s="9">
-        <v>60057</v>
-      </c>
-      <c r="XU24" s="9">
-        <v>57266</v>
-      </c>
-      <c r="XV24" s="9">
-        <v>57132</v>
-      </c>
-      <c r="XW24" s="9">
-        <v>54407</v>
-      </c>
-      <c r="XX24" s="9">
-        <v>52992</v>
-      </c>
-      <c r="XY24" s="9">
-        <v>48318</v>
-      </c>
-      <c r="XZ24" s="9">
-        <v>46936</v>
-      </c>
-      <c r="YA24" s="9">
-        <v>42238</v>
-      </c>
-      <c r="YB24" s="9">
-        <v>39673</v>
-      </c>
-      <c r="YC24" s="9">
-        <v>36671</v>
-      </c>
-      <c r="YD24" s="9">
-        <v>32788</v>
-      </c>
-      <c r="YE24" s="9">
-        <v>29336</v>
-      </c>
-      <c r="YF24" s="9">
-        <v>24849</v>
-      </c>
-      <c r="YG24" s="9">
-        <v>22744</v>
-      </c>
-      <c r="YH24" s="9">
-        <v>19464</v>
-      </c>
-      <c r="YI24" s="9">
-        <v>12916</v>
-      </c>
-      <c r="YJ24" s="9">
-        <v>9880</v>
-      </c>
-      <c r="YK24" s="9">
-        <v>7754</v>
-      </c>
-      <c r="YL24" s="9">
-        <v>5526</v>
-      </c>
-      <c r="YM24" s="9">
-        <v>3845</v>
-      </c>
-      <c r="YN24" s="9">
-        <v>2892</v>
-      </c>
-      <c r="YO24" s="9">
-        <v>1939</v>
-      </c>
-      <c r="YP24" s="9">
-        <v>1280</v>
-      </c>
-      <c r="YQ24" s="9">
-        <v>123226</v>
-      </c>
-      <c r="YR24" s="9">
-        <v>123668</v>
-      </c>
-      <c r="YS24" s="9">
-        <v>121512</v>
-      </c>
-      <c r="YT24" s="9">
-        <v>118171</v>
-      </c>
-      <c r="YU24" s="9">
-        <v>109354</v>
-      </c>
-      <c r="YV24" s="9">
-        <v>99169</v>
-      </c>
-      <c r="YW24" s="9">
-        <v>86438</v>
-      </c>
-      <c r="YX24" s="9">
-        <v>81285</v>
-      </c>
-      <c r="YY24" s="9">
-        <v>80145</v>
-      </c>
-      <c r="YZ24" s="9">
-        <v>75556</v>
-      </c>
-      <c r="ZA24" s="9">
-        <v>70267</v>
-      </c>
-      <c r="ZB24" s="9">
-        <v>66606</v>
-      </c>
-      <c r="ZC24" s="9">
-        <v>61725</v>
-      </c>
-      <c r="ZD24" s="9">
-        <v>57911</v>
-      </c>
-      <c r="ZE24" s="9">
-        <v>55102</v>
-      </c>
-      <c r="ZF24" s="9">
-        <v>54609</v>
-      </c>
-      <c r="ZG24" s="9">
-        <v>51703</v>
-      </c>
-      <c r="ZH24" s="9">
-        <v>50073</v>
-      </c>
-      <c r="ZI24" s="9">
-        <v>45210</v>
-      </c>
-      <c r="ZJ24" s="9">
-        <v>43585</v>
-      </c>
-      <c r="ZK24" s="9">
-        <v>38763</v>
-      </c>
-      <c r="ZL24" s="9">
-        <v>35969</v>
-      </c>
-      <c r="ZM24" s="9">
-        <v>32799</v>
-      </c>
-      <c r="ZN24" s="9">
-        <v>28890</v>
-      </c>
-      <c r="ZO24" s="9">
-        <v>25315</v>
-      </c>
-      <c r="ZP24" s="9">
-        <v>21024</v>
-      </c>
-      <c r="ZQ24" s="9">
-        <v>18973</v>
-      </c>
-      <c r="ZR24" s="9">
-        <v>15878</v>
-      </c>
-      <c r="ZS24" s="9">
-        <v>10256</v>
-      </c>
-      <c r="ZT24" s="9">
-        <v>7544</v>
-      </c>
-      <c r="ZU24" s="9">
-        <v>5779</v>
-      </c>
-      <c r="ZV24" s="9">
-        <v>4008</v>
-      </c>
-      <c r="ZW24" s="9">
-        <v>2685</v>
-      </c>
-      <c r="ZX24" s="9">
-        <v>1968</v>
-      </c>
-      <c r="ZY24" s="9">
-        <v>1281</v>
-      </c>
-      <c r="ZZ24" s="9">
-        <v>121945</v>
-      </c>
-      <c r="AAA24" s="9">
-        <v>122064</v>
-      </c>
-      <c r="AAB24" s="9">
-        <v>122449</v>
-      </c>
-      <c r="AAC24" s="9">
-        <v>120131</v>
-      </c>
-      <c r="AAD24" s="9">
-        <v>116767</v>
-      </c>
-      <c r="AAE24" s="9">
-        <v>107858</v>
-      </c>
-      <c r="AAF24" s="9">
-        <v>97649</v>
-      </c>
-      <c r="AAG24" s="9">
-        <v>85029</v>
-      </c>
-      <c r="AAH24" s="9">
-        <v>79797</v>
-      </c>
-      <c r="AAI24" s="9">
-        <v>78497</v>
-      </c>
-      <c r="AAJ24" s="9">
-        <v>73736</v>
-      </c>
-      <c r="AAK24" s="9">
-        <v>68405</v>
-      </c>
-      <c r="AAL24" s="9">
-        <v>64634</v>
-      </c>
-      <c r="AAM24" s="9">
-        <v>59719</v>
-      </c>
-      <c r="AAN24" s="9">
-        <v>55810</v>
-      </c>
-      <c r="AAO24" s="9">
-        <v>52721</v>
-      </c>
-      <c r="AAP24" s="9">
-        <v>51954</v>
-      </c>
-      <c r="AAQ24" s="9">
-        <v>48943</v>
-      </c>
-      <c r="AAR24" s="9">
-        <v>47027</v>
-      </c>
-      <c r="AAS24" s="9">
-        <v>42043</v>
-      </c>
-      <c r="AAT24" s="9">
-        <v>40125</v>
-      </c>
-      <c r="AAU24" s="9">
-        <v>35319</v>
-      </c>
-      <c r="AAV24" s="9">
-        <v>32394</v>
-      </c>
-      <c r="AAW24" s="9">
-        <v>29097</v>
-      </c>
-      <c r="AAX24" s="9">
-        <v>25079</v>
-      </c>
-      <c r="AAY24" s="9">
-        <v>21604</v>
-      </c>
-      <c r="AAZ24" s="9">
-        <v>17571</v>
-      </c>
-      <c r="ABA24" s="9">
-        <v>15371</v>
-      </c>
-      <c r="ABB24" s="9">
-        <v>12725</v>
-      </c>
-      <c r="ABC24" s="9">
-        <v>7985</v>
-      </c>
-      <c r="ABD24" s="9">
-        <v>5716</v>
-      </c>
-      <c r="ABE24" s="9">
-        <v>4222</v>
-      </c>
-      <c r="ABF24" s="9">
-        <v>2843</v>
-      </c>
-      <c r="ABG24" s="9">
-        <v>1798</v>
-      </c>
-      <c r="ABH24" s="9">
-        <v>1301</v>
-      </c>
-      <c r="ABI24" s="9">
-        <v>117762</v>
-      </c>
-      <c r="ABJ24" s="9">
-        <v>120825</v>
-      </c>
-      <c r="ABK24" s="9">
-        <v>120826</v>
-      </c>
-      <c r="ABL24" s="9">
-        <v>121041</v>
-      </c>
-      <c r="ABM24" s="9">
-        <v>118684</v>
-      </c>
-      <c r="ABN24" s="9">
-        <v>115197</v>
-      </c>
-      <c r="ABO24" s="9">
-        <v>106231</v>
-      </c>
-      <c r="ABP24" s="9">
-        <v>96069</v>
-      </c>
-      <c r="ABQ24" s="9">
-        <v>83575</v>
-      </c>
-      <c r="ABR24" s="9">
-        <v>78185</v>
-      </c>
-      <c r="ABS24" s="9">
-        <v>76680</v>
-      </c>
-      <c r="ABT24" s="9">
-        <v>71869</v>
-      </c>
-      <c r="ABU24" s="9">
-        <v>66386</v>
-      </c>
-      <c r="ABV24" s="9">
-        <v>62541</v>
-      </c>
-      <c r="ABW24" s="9">
-        <v>57605</v>
-      </c>
-      <c r="ABX24" s="9">
-        <v>53606</v>
-      </c>
-      <c r="ABY24" s="9">
-        <v>50319</v>
-      </c>
-      <c r="ABZ24" s="9">
-        <v>49195</v>
-      </c>
-      <c r="ACA24" s="9">
-        <v>46047</v>
-      </c>
-      <c r="ACB24" s="9">
-        <v>43757</v>
-      </c>
-      <c r="ACC24" s="9">
-        <v>38810</v>
-      </c>
-      <c r="ACD24" s="9">
-        <v>36558</v>
-      </c>
-      <c r="ACE24" s="9">
-        <v>31865</v>
-      </c>
-      <c r="ACF24" s="9">
-        <v>28761</v>
-      </c>
-      <c r="ACG24" s="9">
-        <v>25494</v>
-      </c>
-      <c r="ACH24" s="9">
-        <v>21568</v>
-      </c>
-      <c r="ACI24" s="9">
-        <v>18171</v>
-      </c>
-      <c r="ACJ24" s="9">
-        <v>14493</v>
-      </c>
-      <c r="ACK24" s="9">
-        <v>12322</v>
-      </c>
-      <c r="ACL24" s="9">
-        <v>9963</v>
-      </c>
-      <c r="ACM24" s="9">
-        <v>6108</v>
-      </c>
-      <c r="ACN24" s="9">
-        <v>4238</v>
-      </c>
-      <c r="ACO24" s="9">
-        <v>3027</v>
-      </c>
-      <c r="ACP24" s="9">
-        <v>1965</v>
-      </c>
-      <c r="ACQ24" s="9">
-        <v>1188</v>
-      </c>
-      <c r="ACR24" s="9">
-        <v>113621</v>
-      </c>
-      <c r="ACS24" s="9">
-        <v>116632</v>
-      </c>
-      <c r="ACT24" s="9">
-        <v>119621</v>
-      </c>
-      <c r="ACU24" s="9">
-        <v>119458</v>
-      </c>
-      <c r="ACV24" s="9">
-        <v>119599</v>
-      </c>
-      <c r="ACW24" s="9">
-        <v>117113</v>
-      </c>
-      <c r="ACX24" s="9">
-        <v>113419</v>
-      </c>
-      <c r="ACY24" s="9">
-        <v>104443</v>
-      </c>
-      <c r="ACZ24" s="9">
-        <v>94357</v>
-      </c>
-      <c r="ADA24" s="9">
-        <v>81837</v>
-      </c>
-      <c r="ADB24" s="9">
-        <v>76379</v>
-      </c>
-      <c r="ADC24" s="9">
-        <v>74708</v>
-      </c>
-      <c r="ADD24" s="9">
-        <v>69855</v>
-      </c>
-      <c r="ADE24" s="9">
-        <v>64245</v>
-      </c>
-      <c r="ADF24" s="9">
-        <v>60290</v>
-      </c>
-      <c r="ADG24" s="9">
-        <v>55244</v>
-      </c>
-      <c r="ADH24" s="9">
-        <v>51049</v>
-      </c>
-      <c r="ADI24" s="9">
-        <v>47728</v>
-      </c>
-      <c r="ADJ24" s="9">
-        <v>46168</v>
-      </c>
-      <c r="ADK24" s="9">
-        <v>42990</v>
-      </c>
-      <c r="ADL24" s="9">
-        <v>40316</v>
-      </c>
-      <c r="ADM24" s="9">
-        <v>35432</v>
-      </c>
-      <c r="ADN24" s="9">
-        <v>32881</v>
-      </c>
-      <c r="ADO24" s="9">
-        <v>28370</v>
-      </c>
-      <c r="ADP24" s="9">
-        <v>25109</v>
-      </c>
-      <c r="ADQ24" s="9">
-        <v>21851</v>
-      </c>
-      <c r="ADR24" s="9">
-        <v>18170</v>
-      </c>
-      <c r="ADS24" s="9">
-        <v>14806</v>
-      </c>
-      <c r="ADT24" s="9">
-        <v>11550</v>
-      </c>
-      <c r="ADU24" s="9">
-        <v>9636</v>
-      </c>
-      <c r="ADV24" s="9">
-        <v>7567</v>
-      </c>
-      <c r="ADW24" s="9">
-        <v>4485</v>
-      </c>
-      <c r="ADX24" s="9">
-        <v>3016</v>
-      </c>
-      <c r="ADY24" s="9">
-        <v>2070</v>
-      </c>
-      <c r="ADZ24" s="9">
-        <v>1316</v>
-      </c>
-      <c r="AEA24" s="9">
-        <v>108662</v>
-      </c>
-      <c r="AEB24" s="9">
-        <v>112625</v>
-      </c>
-      <c r="AEC24" s="9">
-        <v>115530</v>
-      </c>
-      <c r="AED24" s="9">
-        <v>118331</v>
-      </c>
-      <c r="AEE24" s="9">
-        <v>118118</v>
-      </c>
-      <c r="AEF24" s="9">
-        <v>117978</v>
-      </c>
-      <c r="AEG24" s="9">
-        <v>115476</v>
-      </c>
-      <c r="AEH24" s="9">
-        <v>111472</v>
-      </c>
-      <c r="AEI24" s="9">
-        <v>102537</v>
-      </c>
-      <c r="AEJ24" s="9">
-        <v>92448</v>
-      </c>
-      <c r="AEK24" s="9">
-        <v>80107</v>
-      </c>
-      <c r="AEL24" s="9">
-        <v>74485</v>
-      </c>
-      <c r="AEM24" s="9">
-        <v>72620</v>
-      </c>
-      <c r="AEN24" s="9">
-        <v>67674</v>
-      </c>
-      <c r="AEO24" s="9">
-        <v>61900</v>
-      </c>
-      <c r="AEP24" s="9">
-        <v>57868</v>
-      </c>
-      <c r="AEQ24" s="9">
-        <v>52646</v>
-      </c>
-      <c r="AER24" s="9">
-        <v>48461</v>
-      </c>
-      <c r="AES24" s="9">
-        <v>44952</v>
-      </c>
-      <c r="AET24" s="9">
-        <v>43103</v>
-      </c>
-      <c r="AEU24" s="9">
-        <v>39712</v>
-      </c>
-      <c r="AEV24" s="9">
-        <v>36789</v>
-      </c>
-      <c r="AEW24" s="9">
-        <v>31966</v>
-      </c>
-      <c r="AEX24" s="9">
-        <v>29224</v>
-      </c>
-      <c r="AEY24" s="9">
-        <v>25054</v>
-      </c>
-      <c r="AEZ24" s="9">
-        <v>21492</v>
-      </c>
-      <c r="AFA24" s="9">
-        <v>18259</v>
-      </c>
-      <c r="AFB24" s="9">
-        <v>14989</v>
-      </c>
-      <c r="AFC24" s="9">
-        <v>11864</v>
-      </c>
-      <c r="AFD24" s="9">
-        <v>8960</v>
-      </c>
-      <c r="AFE24" s="9">
-        <v>7369</v>
-      </c>
-      <c r="AFF24" s="9">
-        <v>5544</v>
-      </c>
-      <c r="AFG24" s="9">
-        <v>3170</v>
-      </c>
-      <c r="AFH24" s="9">
-        <v>2065</v>
-      </c>
-      <c r="AFI24" s="9">
-        <v>1426</v>
-      </c>
-      <c r="AFJ24" s="9">
-        <v>109841</v>
-      </c>
-      <c r="AFK24" s="9">
-        <v>107721</v>
-      </c>
-      <c r="AFL24" s="9">
-        <v>111517</v>
-      </c>
-      <c r="AFM24" s="9">
-        <v>114318</v>
-      </c>
-      <c r="AFN24" s="9">
-        <v>116995</v>
-      </c>
-      <c r="AFO24" s="9">
-        <v>116520</v>
-      </c>
-      <c r="AFP24" s="9">
-        <v>116256</v>
-      </c>
-      <c r="AFQ24" s="9">
-        <v>113660</v>
-      </c>
-      <c r="AFR24" s="9">
-        <v>109518</v>
-      </c>
-      <c r="AFS24" s="9">
-        <v>100530</v>
-      </c>
-      <c r="AFT24" s="9">
-        <v>90457</v>
-      </c>
-      <c r="AFU24" s="9">
-        <v>78171</v>
-      </c>
-      <c r="AFV24" s="9">
-        <v>72401</v>
-      </c>
-      <c r="AFW24" s="9">
-        <v>70284</v>
-      </c>
-      <c r="AFX24" s="9">
-        <v>65287</v>
-      </c>
-      <c r="AFY24" s="9">
-        <v>59491</v>
-      </c>
-      <c r="AFZ24" s="9">
-        <v>55248</v>
-      </c>
-      <c r="AGA24" s="9">
-        <v>49960</v>
-      </c>
-      <c r="AGB24" s="9">
-        <v>45542</v>
-      </c>
-      <c r="AGC24" s="9">
-        <v>41880</v>
-      </c>
-      <c r="AGD24" s="9">
-        <v>39850</v>
-      </c>
-      <c r="AGE24" s="9">
-        <v>36338</v>
-      </c>
-      <c r="AGF24" s="9">
-        <v>33148</v>
-      </c>
-      <c r="AGG24" s="9">
-        <v>28337</v>
-      </c>
-      <c r="AGH24" s="9">
-        <v>25492</v>
-      </c>
-      <c r="AGI24" s="9">
-        <v>21393</v>
-      </c>
-      <c r="AGJ24" s="9">
-        <v>18054</v>
-      </c>
-      <c r="AGK24" s="9">
-        <v>15005</v>
-      </c>
-      <c r="AGL24" s="9">
-        <v>12021</v>
-      </c>
-      <c r="AGM24" s="9">
-        <v>9247</v>
-      </c>
-      <c r="AGN24" s="9">
-        <v>6749</v>
-      </c>
-      <c r="AGO24" s="9">
-        <v>5400</v>
-      </c>
-      <c r="AGP24" s="9">
-        <v>3968</v>
-      </c>
-      <c r="AGQ24" s="9">
-        <v>2132</v>
-      </c>
-      <c r="AGR24" s="9">
-        <v>1331</v>
-      </c>
-      <c r="AGS24" s="9">
-        <v>110550</v>
-      </c>
-      <c r="AGT24" s="9">
-        <v>108902</v>
-      </c>
-      <c r="AGU24" s="9">
-        <v>106604</v>
-      </c>
-      <c r="AGV24" s="9">
-        <v>110308</v>
-      </c>
-      <c r="AGW24" s="9">
-        <v>112947</v>
-      </c>
-      <c r="AGX24" s="9">
-        <v>115428</v>
-      </c>
-      <c r="AGY24" s="9">
-        <v>114877</v>
-      </c>
-      <c r="AGZ24" s="9">
-        <v>114340</v>
-      </c>
-      <c r="AHA24" s="9">
-        <v>111644</v>
-      </c>
-      <c r="AHB24" s="9">
-        <v>107359</v>
-      </c>
-      <c r="AHC24" s="9">
-        <v>98295</v>
-      </c>
-      <c r="AHD24" s="9">
-        <v>88283</v>
-      </c>
-      <c r="AHE24" s="9">
-        <v>76006</v>
-      </c>
-      <c r="AHF24" s="9">
-        <v>70129</v>
-      </c>
-      <c r="AHG24" s="9">
-        <v>67906</v>
-      </c>
-      <c r="AHH24" s="9">
-        <v>62709</v>
-      </c>
-      <c r="AHI24" s="9">
-        <v>56824</v>
-      </c>
-      <c r="AHJ24" s="9">
-        <v>52406</v>
-      </c>
-      <c r="AHK24" s="9">
-        <v>47049</v>
-      </c>
-      <c r="AHL24" s="9">
-        <v>42539</v>
-      </c>
-      <c r="AHM24" s="9">
-        <v>38765</v>
-      </c>
-      <c r="AHN24" s="9">
-        <v>36446</v>
-      </c>
-      <c r="AHO24" s="9">
-        <v>32839</v>
-      </c>
-      <c r="AHP24" s="9">
-        <v>29472</v>
-      </c>
-      <c r="AHQ24" s="9">
-        <v>24781</v>
-      </c>
-      <c r="AHR24" s="9">
-        <v>21788</v>
-      </c>
-      <c r="AHS24" s="9">
-        <v>18013</v>
-      </c>
-      <c r="AHT24" s="9">
-        <v>14932</v>
-      </c>
-      <c r="AHU24" s="9">
-        <v>12034</v>
-      </c>
-      <c r="AHV24" s="9">
-        <v>9480</v>
-      </c>
-      <c r="AHW24" s="9">
-        <v>7006</v>
-      </c>
-      <c r="AHX24" s="9">
-        <v>4983</v>
-      </c>
-      <c r="AHY24" s="9">
-        <v>3873</v>
-      </c>
-      <c r="AHZ24" s="9">
-        <v>2724</v>
-      </c>
-      <c r="AIA24" s="9">
-        <v>1403</v>
-      </c>
-      <c r="AIB24" s="9">
-        <v>108095</v>
-      </c>
-      <c r="AIC24" s="9">
-        <v>109510</v>
-      </c>
-      <c r="AID24" s="9">
-        <v>107927</v>
-      </c>
-      <c r="AIE24" s="9">
-        <v>105509</v>
-      </c>
-      <c r="AIF24" s="9">
-        <v>109007</v>
-      </c>
-      <c r="AIG24" s="9">
-        <v>111522</v>
-      </c>
-      <c r="AIH24" s="9">
-        <v>113904</v>
-      </c>
-      <c r="AII24" s="9">
-        <v>113141</v>
-      </c>
-      <c r="AIJ24" s="9">
-        <v>112310</v>
-      </c>
-      <c r="AIK24" s="9">
-        <v>109538</v>
-      </c>
-      <c r="AIL24" s="9">
-        <v>105077</v>
-      </c>
-      <c r="AIM24" s="9">
-        <v>95932</v>
-      </c>
-      <c r="AIN24" s="9">
-        <v>85993</v>
-      </c>
-      <c r="AIO24" s="9">
-        <v>73767</v>
-      </c>
-      <c r="AIP24" s="9">
-        <v>67829</v>
-      </c>
-      <c r="AIQ24" s="9">
-        <v>65302</v>
-      </c>
-      <c r="AIR24" s="9">
-        <v>60124</v>
-      </c>
-      <c r="AIS24" s="9">
-        <v>54029</v>
-      </c>
-      <c r="AIT24" s="9">
-        <v>49510</v>
-      </c>
-      <c r="AIU24" s="9">
-        <v>44085</v>
-      </c>
-      <c r="AIV24" s="9">
-        <v>39486</v>
-      </c>
-      <c r="AIW24" s="9">
-        <v>35646</v>
-      </c>
-      <c r="AIX24" s="9">
-        <v>33049</v>
-      </c>
-      <c r="AIY24" s="9">
-        <v>29430</v>
-      </c>
-      <c r="AIZ24" s="9">
-        <v>26018</v>
-      </c>
-      <c r="AJA24" s="9">
-        <v>21450</v>
-      </c>
-      <c r="AJB24" s="9">
-        <v>18531</v>
-      </c>
-      <c r="AJC24" s="9">
-        <v>15006</v>
-      </c>
-      <c r="AJD24" s="9">
-        <v>12119</v>
-      </c>
-      <c r="AJE24" s="9">
-        <v>9538</v>
-      </c>
-      <c r="AJF24" s="9">
-        <v>7317</v>
-      </c>
-      <c r="AJG24" s="9">
-        <v>5241</v>
-      </c>
-      <c r="AJH24" s="9">
-        <v>3655</v>
-      </c>
-      <c r="AJI24" s="9">
-        <v>2709</v>
-      </c>
-      <c r="AJJ24" s="9">
-        <v>1854</v>
-      </c>
-      <c r="AJK24" s="9">
-        <v>110223</v>
-      </c>
-      <c r="AJL24" s="9">
-        <v>107098</v>
-      </c>
-      <c r="AJM24" s="9">
-        <v>108404</v>
-      </c>
-      <c r="AJN24" s="9">
-        <v>106751</v>
-      </c>
-      <c r="AJO24" s="9">
-        <v>104258</v>
-      </c>
-      <c r="AJP24" s="9">
-        <v>107566</v>
-      </c>
-      <c r="AJQ24" s="9">
-        <v>109846</v>
-      </c>
-      <c r="AJR24" s="9">
-        <v>112058</v>
-      </c>
-      <c r="AJS24" s="9">
-        <v>111095</v>
-      </c>
-      <c r="AJT24" s="9">
-        <v>110052</v>
-      </c>
-      <c r="AJU24" s="9">
-        <v>107099</v>
-      </c>
-      <c r="AJV24" s="9">
-        <v>102442</v>
-      </c>
-      <c r="AJW24" s="9">
-        <v>93151</v>
-      </c>
-      <c r="AJX24" s="9">
-        <v>83344</v>
-      </c>
-      <c r="AJY24" s="9">
-        <v>70979</v>
-      </c>
-      <c r="AJZ24" s="9">
-        <v>65042</v>
-      </c>
-      <c r="AKA24" s="9">
-        <v>62228</v>
-      </c>
-      <c r="AKB24" s="9">
-        <v>56875</v>
-      </c>
-      <c r="AKC24" s="9">
-        <v>50651</v>
-      </c>
-      <c r="AKD24" s="9">
-        <v>46234</v>
-      </c>
-      <c r="AKE24" s="9">
-        <v>40534</v>
-      </c>
-      <c r="AKF24" s="9">
-        <v>35935</v>
-      </c>
-      <c r="AKG24" s="9">
-        <v>32151</v>
-      </c>
-      <c r="AKH24" s="9">
-        <v>29194</v>
-      </c>
-      <c r="AKI24" s="9">
-        <v>25560</v>
-      </c>
-      <c r="AKJ24" s="9">
-        <v>22125</v>
-      </c>
-      <c r="AKK24" s="9">
-        <v>17922</v>
-      </c>
-      <c r="AKL24" s="9">
-        <v>15086</v>
-      </c>
-      <c r="AKM24" s="9">
-        <v>11928</v>
-      </c>
-      <c r="AKN24" s="9">
-        <v>9315</v>
-      </c>
-      <c r="AKO24" s="9">
-        <v>7135</v>
-      </c>
-      <c r="AKP24" s="9">
-        <v>5361</v>
-      </c>
-      <c r="AKQ24" s="9">
-        <v>3710</v>
-      </c>
-      <c r="AKR24" s="9">
-        <v>2515</v>
-      </c>
-      <c r="AKS24" s="9">
-        <v>1770</v>
-      </c>
-      <c r="AKT24" s="9">
-        <v>112116</v>
-      </c>
-      <c r="AKU24" s="9">
-        <v>109244</v>
-      </c>
-      <c r="AKV24" s="9">
-        <v>106045</v>
-      </c>
-      <c r="AKW24" s="9">
-        <v>107279</v>
-      </c>
-      <c r="AKX24" s="9">
-        <v>105536</v>
-      </c>
-      <c r="AKY24" s="9">
-        <v>102886</v>
-      </c>
-      <c r="AKZ24" s="9">
-        <v>105990</v>
-      </c>
-      <c r="ALA24" s="9">
-        <v>108111</v>
-      </c>
-      <c r="ALB24" s="9">
-        <v>110180</v>
-      </c>
-      <c r="ALC24" s="9">
-        <v>108949</v>
-      </c>
-      <c r="ALD24" s="9">
-        <v>107685</v>
-      </c>
-      <c r="ALE24" s="9">
-        <v>104546</v>
-      </c>
-      <c r="ALF24" s="9">
-        <v>99697</v>
-      </c>
-      <c r="ALG24" s="9">
-        <v>90315</v>
-      </c>
-      <c r="ALH24" s="9">
-        <v>80553</v>
-      </c>
-      <c r="ALI24" s="9">
-        <v>68279</v>
-      </c>
-      <c r="ALJ24" s="9">
-        <v>62285</v>
-      </c>
-      <c r="ALK24" s="9">
-        <v>59265</v>
-      </c>
-      <c r="ALL24" s="9">
-        <v>53748</v>
-      </c>
-      <c r="ALM24" s="9">
-        <v>47434</v>
-      </c>
-      <c r="ALN24" s="9">
-        <v>42966</v>
-      </c>
-      <c r="ALO24" s="9">
-        <v>37186</v>
-      </c>
-      <c r="ALP24" s="9">
-        <v>32671</v>
-      </c>
-      <c r="ALQ24" s="9">
-        <v>28783</v>
-      </c>
-      <c r="ALR24" s="9">
-        <v>25715</v>
-      </c>
-      <c r="ALS24" s="9">
-        <v>22208</v>
-      </c>
-      <c r="ALT24" s="9">
-        <v>18804</v>
-      </c>
-      <c r="ALU24" s="9">
-        <v>14969</v>
-      </c>
-      <c r="ALV24" s="9">
-        <v>12268</v>
-      </c>
-      <c r="ALW24" s="9">
-        <v>9499</v>
-      </c>
-      <c r="ALX24" s="9">
-        <v>7236</v>
-      </c>
-      <c r="ALY24" s="9">
-        <v>5344</v>
-      </c>
-      <c r="ALZ24" s="9">
-        <v>3944</v>
-      </c>
-      <c r="AMA24" s="9">
-        <v>2639</v>
-      </c>
-      <c r="AMB24" s="9">
-        <v>1729</v>
-      </c>
-      <c r="AMC24" s="9">
-        <v>112055</v>
-      </c>
-      <c r="AMD24" s="9">
-        <v>111275</v>
-      </c>
-      <c r="AME24" s="9">
-        <v>108290</v>
-      </c>
-      <c r="AMF24" s="9">
-        <v>104990</v>
-      </c>
-      <c r="AMG24" s="9">
-        <v>106130</v>
-      </c>
-      <c r="AMH24" s="9">
-        <v>104165</v>
-      </c>
-      <c r="AMI24" s="9">
-        <v>101489</v>
-      </c>
-      <c r="AMJ24" s="9">
-        <v>104335</v>
-      </c>
-      <c r="AMK24" s="9">
-        <v>106311</v>
-      </c>
-      <c r="AML24" s="9">
-        <v>108083</v>
-      </c>
-      <c r="AMM24" s="9">
-        <v>106730</v>
-      </c>
-      <c r="AMN24" s="9">
-        <v>105197</v>
-      </c>
-      <c r="AMO24" s="9">
-        <v>101810</v>
-      </c>
-      <c r="AMP24" s="9">
-        <v>96645</v>
-      </c>
-      <c r="AMQ24" s="9">
-        <v>87285</v>
-      </c>
-      <c r="AMR24" s="9">
-        <v>77551</v>
-      </c>
-      <c r="AMS24" s="9">
-        <v>65310</v>
-      </c>
-      <c r="AMT24" s="9">
-        <v>59186</v>
-      </c>
-      <c r="AMU24" s="9">
-        <v>55885</v>
-      </c>
-      <c r="AMV24" s="9">
-        <v>50399</v>
-      </c>
-      <c r="AMW24" s="9">
-        <v>44024</v>
-      </c>
-      <c r="AMX24" s="9">
-        <v>39516</v>
-      </c>
-      <c r="AMY24" s="9">
-        <v>33810</v>
-      </c>
-      <c r="AMZ24" s="9">
-        <v>29260</v>
-      </c>
-      <c r="ANA24" s="9">
-        <v>25343</v>
-      </c>
-      <c r="ANB24" s="9">
-        <v>22313</v>
-      </c>
-      <c r="ANC24" s="9">
-        <v>18751</v>
-      </c>
-      <c r="AND24" s="9">
-        <v>15599</v>
-      </c>
-      <c r="ANE24" s="9">
-        <v>12078</v>
-      </c>
-      <c r="ANF24" s="9">
-        <v>9646</v>
-      </c>
-      <c r="ANG24" s="9">
-        <v>7263</v>
-      </c>
-      <c r="ANH24" s="9">
-        <v>5413</v>
-      </c>
-      <c r="ANI24" s="9">
-        <v>3811</v>
-      </c>
-      <c r="ANJ24" s="9">
-        <v>2733</v>
-      </c>
-      <c r="ANK24" s="9">
-        <v>1769</v>
-      </c>
-      <c r="ANL24" s="9">
-        <v>111147</v>
-      </c>
-      <c r="ANM24" s="9">
-        <v>111138</v>
-      </c>
-      <c r="ANN24" s="9">
-        <v>110302</v>
-      </c>
-      <c r="ANO24" s="9">
-        <v>107262</v>
-      </c>
-      <c r="ANP24" s="9">
-        <v>103870</v>
-      </c>
-      <c r="ANQ24" s="9">
-        <v>104851</v>
-      </c>
-      <c r="ANR24" s="9">
-        <v>102805</v>
-      </c>
-      <c r="ANS24" s="9">
-        <v>99923</v>
-      </c>
-      <c r="ANT24" s="9">
-        <v>102660</v>
-      </c>
-      <c r="ANU24" s="9">
-        <v>104398</v>
-      </c>
-      <c r="ANV24" s="9">
-        <v>105825</v>
-      </c>
-      <c r="ANW24" s="9">
-        <v>104266</v>
-      </c>
-      <c r="ANX24" s="9">
-        <v>102537</v>
-      </c>
-      <c r="ANY24" s="9">
-        <v>98769</v>
-      </c>
-      <c r="ANZ24" s="9">
-        <v>93443</v>
-      </c>
-      <c r="AOA24" s="9">
-        <v>84121</v>
-      </c>
-      <c r="AOB24" s="9">
-        <v>74402</v>
-      </c>
-      <c r="AOC24" s="9">
-        <v>62214</v>
-      </c>
-      <c r="AOD24" s="9">
-        <v>56046</v>
-      </c>
-      <c r="AOE24" s="9">
-        <v>52464</v>
-      </c>
-      <c r="AOF24" s="9">
-        <v>46932</v>
-      </c>
-      <c r="AOG24" s="9">
-        <v>40534</v>
-      </c>
-      <c r="AOH24" s="9">
-        <v>35960</v>
-      </c>
-      <c r="AOI24" s="9">
-        <v>30336</v>
-      </c>
-      <c r="AOJ24" s="9">
-        <v>25863</v>
-      </c>
-      <c r="AOK24" s="9">
-        <v>22020</v>
-      </c>
-      <c r="AOL24" s="9">
-        <v>19021</v>
-      </c>
-      <c r="AOM24" s="9">
-        <v>15606</v>
-      </c>
-      <c r="AON24" s="9">
-        <v>12604</v>
-      </c>
-      <c r="AOO24" s="9">
-        <v>9570</v>
-      </c>
-      <c r="AOP24" s="9">
-        <v>7339</v>
-      </c>
-      <c r="AOQ24" s="9">
-        <v>5382</v>
-      </c>
-      <c r="AOR24" s="9">
-        <v>3855</v>
-      </c>
-      <c r="AOS24" s="9">
-        <v>2674</v>
-      </c>
-      <c r="AOT24" s="9">
-        <v>1863</v>
-      </c>
+    <row r="24" spans="1:1086" x14ac:dyDescent="0.3">
+      <c r="A24" s="1"/>
     </row>
     <row r="25" spans="1:1086" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
-    </row>
-    <row r="26" spans="1:1086" x14ac:dyDescent="0.3">
-      <c r="A26" s="1"/>
-      <c r="B26" s="2"/>
+      <c r="B25" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="31">
